--- a/SupervisorMobility.API/DataAccess/Templates/Distribution Template.xlsx
+++ b/SupervisorMobility.API/DataAccess/Templates/Distribution Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ituriel\OneDrive\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{445E593A-7B0D-4F0F-9D27-64D37C0AC894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98C057C8-2466-4837-B00B-6A48BCDFBF11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="52740" yWindow="4365" windowWidth="23235" windowHeight="10950" xr2:uid="{443068A0-8518-4967-88E9-3028C04BF0EC}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="18672" windowHeight="10320" xr2:uid="{443068A0-8518-4967-88E9-3028C04BF0EC}"/>
   </bookViews>
   <sheets>
     <sheet name="HOE DISTRIBUTION" sheetId="1" r:id="rId1"/>
@@ -808,7 +808,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -843,94 +842,201 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -967,42 +1073,24 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1015,149 +1103,77 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1547,33 +1563,33 @@
       <c r="Z1" s="3"/>
     </row>
     <row r="2" spans="2:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="112" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
-      <c r="T2" s="30"/>
-      <c r="U2" s="30"/>
-      <c r="V2" s="30"/>
-      <c r="W2" s="30"/>
-      <c r="X2" s="30"/>
-      <c r="Y2" s="30"/>
-      <c r="Z2" s="30"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
+      <c r="E2" s="112"/>
+      <c r="F2" s="112"/>
+      <c r="G2" s="112"/>
+      <c r="H2" s="112"/>
+      <c r="I2" s="112"/>
+      <c r="J2" s="112"/>
+      <c r="K2" s="112"/>
+      <c r="L2" s="112"/>
+      <c r="M2" s="112"/>
+      <c r="N2" s="112"/>
+      <c r="O2" s="112"/>
+      <c r="P2" s="112"/>
+      <c r="Q2" s="112"/>
+      <c r="R2" s="112"/>
+      <c r="S2" s="112"/>
+      <c r="T2" s="112"/>
+      <c r="U2" s="112"/>
+      <c r="V2" s="112"/>
+      <c r="W2" s="112"/>
+      <c r="X2" s="112"/>
+      <c r="Y2" s="112"/>
+      <c r="Z2" s="112"/>
     </row>
     <row r="3" spans="2:26" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="3"/>
@@ -1684,200 +1700,200 @@
       <c r="Z6" s="3"/>
     </row>
     <row r="7" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="117" t="s">
+      <c r="B7" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="118"/>
-      <c r="D7" s="118"/>
-      <c r="E7" s="118"/>
-      <c r="F7" s="119"/>
-      <c r="G7" s="109" t="s">
+      <c r="C7" s="69"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="69"/>
+      <c r="F7" s="70"/>
+      <c r="G7" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="H7" s="110"/>
-      <c r="I7" s="110"/>
-      <c r="J7" s="110"/>
-      <c r="K7" s="42" t="s">
+      <c r="H7" s="63"/>
+      <c r="I7" s="63"/>
+      <c r="J7" s="63"/>
+      <c r="K7" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="L7" s="86"/>
-      <c r="M7" s="39" t="s">
+      <c r="L7" s="39"/>
+      <c r="M7" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="N7" s="39"/>
-      <c r="O7" s="39"/>
-      <c r="P7" s="39"/>
-      <c r="Q7" s="39"/>
-      <c r="R7" s="39"/>
-      <c r="S7" s="39"/>
-      <c r="T7" s="39"/>
-      <c r="U7" s="39"/>
-      <c r="V7" s="42" t="s">
+      <c r="N7" s="75"/>
+      <c r="O7" s="75"/>
+      <c r="P7" s="75"/>
+      <c r="Q7" s="75"/>
+      <c r="R7" s="75"/>
+      <c r="S7" s="75"/>
+      <c r="T7" s="75"/>
+      <c r="U7" s="75"/>
+      <c r="V7" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="W7" s="43"/>
-      <c r="X7" s="43"/>
-      <c r="Y7" s="43"/>
-      <c r="Z7" s="44"/>
+      <c r="W7" s="121"/>
+      <c r="X7" s="121"/>
+      <c r="Y7" s="121"/>
+      <c r="Z7" s="122"/>
     </row>
     <row r="8" spans="2:26" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B8" s="120"/>
-      <c r="C8" s="121"/>
-      <c r="D8" s="121"/>
-      <c r="E8" s="121"/>
-      <c r="F8" s="122"/>
-      <c r="G8" s="111"/>
-      <c r="H8" s="112"/>
-      <c r="I8" s="112"/>
-      <c r="J8" s="112"/>
-      <c r="K8" s="87"/>
-      <c r="L8" s="88"/>
-      <c r="M8" s="40"/>
-      <c r="N8" s="26"/>
-      <c r="O8" s="26"/>
-      <c r="P8" s="26"/>
-      <c r="Q8" s="26"/>
-      <c r="R8" s="26"/>
-      <c r="S8" s="26"/>
-      <c r="T8" s="26"/>
-      <c r="U8" s="41"/>
-      <c r="V8" s="24"/>
-      <c r="W8" s="24"/>
-      <c r="X8" s="24"/>
-      <c r="Y8" s="24"/>
-      <c r="Z8" s="25"/>
+      <c r="B8" s="71"/>
+      <c r="C8" s="72"/>
+      <c r="D8" s="72"/>
+      <c r="E8" s="72"/>
+      <c r="F8" s="73"/>
+      <c r="G8" s="64"/>
+      <c r="H8" s="65"/>
+      <c r="I8" s="65"/>
+      <c r="J8" s="65"/>
+      <c r="K8" s="40"/>
+      <c r="L8" s="41"/>
+      <c r="M8" s="59"/>
+      <c r="N8" s="60"/>
+      <c r="O8" s="60"/>
+      <c r="P8" s="60"/>
+      <c r="Q8" s="60"/>
+      <c r="R8" s="60"/>
+      <c r="S8" s="60"/>
+      <c r="T8" s="60"/>
+      <c r="U8" s="61"/>
+      <c r="V8" s="107"/>
+      <c r="W8" s="107"/>
+      <c r="X8" s="107"/>
+      <c r="Y8" s="107"/>
+      <c r="Z8" s="108"/>
     </row>
     <row r="9" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B9" s="123" t="s">
+      <c r="B9" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="107"/>
-      <c r="D9" s="108"/>
-      <c r="E9" s="106" t="s">
+      <c r="C9" s="30"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="F9" s="108"/>
-      <c r="G9" s="106" t="s">
+      <c r="F9" s="31"/>
+      <c r="G9" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="H9" s="107"/>
-      <c r="I9" s="107"/>
-      <c r="J9" s="108"/>
-      <c r="K9" s="89"/>
-      <c r="L9" s="90"/>
-      <c r="M9" s="40"/>
-      <c r="N9" s="26"/>
-      <c r="O9" s="26"/>
-      <c r="P9" s="26"/>
-      <c r="Q9" s="26"/>
-      <c r="R9" s="26"/>
-      <c r="S9" s="26"/>
-      <c r="T9" s="26"/>
-      <c r="U9" s="41"/>
-      <c r="V9" s="26"/>
-      <c r="W9" s="26"/>
-      <c r="X9" s="26"/>
-      <c r="Y9" s="26"/>
-      <c r="Z9" s="27"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="42"/>
+      <c r="L9" s="43"/>
+      <c r="M9" s="59"/>
+      <c r="N9" s="60"/>
+      <c r="O9" s="60"/>
+      <c r="P9" s="60"/>
+      <c r="Q9" s="60"/>
+      <c r="R9" s="60"/>
+      <c r="S9" s="60"/>
+      <c r="T9" s="60"/>
+      <c r="U9" s="61"/>
+      <c r="V9" s="60"/>
+      <c r="W9" s="60"/>
+      <c r="X9" s="60"/>
+      <c r="Y9" s="60"/>
+      <c r="Z9" s="109"/>
     </row>
     <row r="10" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B10" s="124"/>
-      <c r="C10" s="71"/>
-      <c r="D10" s="72"/>
-      <c r="E10" s="125"/>
-      <c r="F10" s="72"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="41"/>
-      <c r="K10" s="91"/>
-      <c r="L10" s="88"/>
-      <c r="M10" s="40"/>
-      <c r="N10" s="26"/>
-      <c r="O10" s="26"/>
-      <c r="P10" s="26"/>
-      <c r="Q10" s="26"/>
-      <c r="R10" s="26"/>
-      <c r="S10" s="26"/>
-      <c r="T10" s="26"/>
-      <c r="U10" s="41"/>
-      <c r="V10" s="28"/>
-      <c r="W10" s="29"/>
-      <c r="X10" s="26"/>
-      <c r="Y10" s="26"/>
-      <c r="Z10" s="27"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="59"/>
+      <c r="H10" s="60"/>
+      <c r="I10" s="60"/>
+      <c r="J10" s="61"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="41"/>
+      <c r="M10" s="59"/>
+      <c r="N10" s="60"/>
+      <c r="O10" s="60"/>
+      <c r="P10" s="60"/>
+      <c r="Q10" s="60"/>
+      <c r="R10" s="60"/>
+      <c r="S10" s="60"/>
+      <c r="T10" s="60"/>
+      <c r="U10" s="61"/>
+      <c r="V10" s="110"/>
+      <c r="W10" s="111"/>
+      <c r="X10" s="60"/>
+      <c r="Y10" s="60"/>
+      <c r="Z10" s="109"/>
     </row>
     <row r="11" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B11" s="126" t="s">
+      <c r="B11" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="127"/>
-      <c r="D11" s="75" t="s">
+      <c r="C11" s="26"/>
+      <c r="D11" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="76"/>
-      <c r="F11" s="127"/>
-      <c r="G11" s="113" t="s">
+      <c r="E11" s="25"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="H11" s="114"/>
-      <c r="I11" s="16" t="s">
+      <c r="H11" s="67"/>
+      <c r="I11" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="J11" s="75" t="s">
+      <c r="J11" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="K11" s="76"/>
-      <c r="L11" s="76"/>
-      <c r="M11" s="76"/>
-      <c r="N11" s="76"/>
-      <c r="O11" s="76"/>
-      <c r="P11" s="48" t="s">
+      <c r="K11" s="25"/>
+      <c r="L11" s="25"/>
+      <c r="M11" s="25"/>
+      <c r="N11" s="25"/>
+      <c r="O11" s="25"/>
+      <c r="P11" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="Q11" s="49"/>
-      <c r="R11" s="49"/>
-      <c r="S11" s="49"/>
-      <c r="T11" s="49"/>
-      <c r="U11" s="48" t="s">
+      <c r="Q11" s="84"/>
+      <c r="R11" s="84"/>
+      <c r="S11" s="84"/>
+      <c r="T11" s="84"/>
+      <c r="U11" s="83" t="s">
         <v>30</v>
       </c>
-      <c r="V11" s="49"/>
-      <c r="W11" s="53"/>
-      <c r="X11" s="54" t="s">
+      <c r="V11" s="84"/>
+      <c r="W11" s="85"/>
+      <c r="X11" s="86" t="s">
         <v>31</v>
       </c>
-      <c r="Y11" s="55"/>
-      <c r="Z11" s="56"/>
+      <c r="Y11" s="87"/>
+      <c r="Z11" s="88"/>
     </row>
     <row r="12" spans="2:26" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="128"/>
-      <c r="C12" s="116"/>
-      <c r="D12" s="115"/>
-      <c r="E12" s="129"/>
-      <c r="F12" s="116"/>
-      <c r="G12" s="115"/>
-      <c r="H12" s="116"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="23"/>
       <c r="I12" s="7"/>
-      <c r="J12" s="50"/>
-      <c r="K12" s="51"/>
-      <c r="L12" s="51"/>
-      <c r="M12" s="51"/>
-      <c r="N12" s="51"/>
-      <c r="O12" s="51"/>
-      <c r="P12" s="50"/>
-      <c r="Q12" s="51"/>
-      <c r="R12" s="51"/>
-      <c r="S12" s="51"/>
-      <c r="T12" s="52"/>
-      <c r="U12" s="50"/>
-      <c r="V12" s="51"/>
-      <c r="W12" s="52"/>
-      <c r="X12" s="22"/>
+      <c r="J12" s="80"/>
+      <c r="K12" s="81"/>
+      <c r="L12" s="81"/>
+      <c r="M12" s="81"/>
+      <c r="N12" s="81"/>
+      <c r="O12" s="81"/>
+      <c r="P12" s="80"/>
+      <c r="Q12" s="81"/>
+      <c r="R12" s="81"/>
+      <c r="S12" s="81"/>
+      <c r="T12" s="82"/>
+      <c r="U12" s="80"/>
+      <c r="V12" s="81"/>
+      <c r="W12" s="82"/>
+      <c r="X12" s="20"/>
       <c r="Y12" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z12" s="23"/>
+      <c r="Z12" s="21"/>
     </row>
     <row r="13" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="3"/>
@@ -1907,199 +1923,229 @@
       <c r="Z13" s="3"/>
     </row>
     <row r="14" spans="2:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="104" t="s">
+      <c r="B14" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="65" t="s">
+      <c r="C14" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="81"/>
-      <c r="H14" s="65" t="s">
+      <c r="D14" s="75"/>
+      <c r="E14" s="75"/>
+      <c r="F14" s="75"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="74" t="s">
         <v>17</v>
       </c>
-      <c r="I14" s="39"/>
-      <c r="J14" s="39"/>
-      <c r="K14" s="81"/>
-      <c r="L14" s="73" t="s">
+      <c r="I14" s="75"/>
+      <c r="J14" s="75"/>
+      <c r="K14" s="76"/>
+      <c r="L14" s="101" t="s">
         <v>16</v>
       </c>
-      <c r="M14" s="74"/>
-      <c r="N14" s="74"/>
-      <c r="O14" s="74"/>
-      <c r="P14" s="74"/>
-      <c r="Q14" s="74"/>
-      <c r="R14" s="65" t="s">
+      <c r="M14" s="102"/>
+      <c r="N14" s="102"/>
+      <c r="O14" s="102"/>
+      <c r="P14" s="102"/>
+      <c r="Q14" s="102"/>
+      <c r="R14" s="74" t="s">
         <v>15</v>
       </c>
-      <c r="S14" s="39"/>
-      <c r="T14" s="39"/>
-      <c r="U14" s="39"/>
-      <c r="V14" s="39"/>
-      <c r="W14" s="39"/>
-      <c r="X14" s="39"/>
-      <c r="Y14" s="39"/>
-      <c r="Z14" s="66"/>
+      <c r="S14" s="75"/>
+      <c r="T14" s="75"/>
+      <c r="U14" s="75"/>
+      <c r="V14" s="75"/>
+      <c r="W14" s="75"/>
+      <c r="X14" s="75"/>
+      <c r="Y14" s="75"/>
+      <c r="Z14" s="97"/>
     </row>
     <row r="15" spans="2:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="105"/>
-      <c r="C15" s="67" t="s">
+      <c r="B15" s="58"/>
+      <c r="C15" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="68"/>
-      <c r="E15" s="68"/>
-      <c r="F15" s="68"/>
-      <c r="G15" s="82"/>
-      <c r="H15" s="67"/>
-      <c r="I15" s="68"/>
-      <c r="J15" s="68"/>
-      <c r="K15" s="82"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17"/>
-      <c r="N15" s="17"/>
-      <c r="O15" s="71"/>
-      <c r="P15" s="72"/>
+      <c r="D15" s="78"/>
+      <c r="E15" s="78"/>
+      <c r="F15" s="78"/>
+      <c r="G15" s="79"/>
+      <c r="H15" s="77"/>
+      <c r="I15" s="78"/>
+      <c r="J15" s="78"/>
+      <c r="K15" s="79"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="35"/>
       <c r="Q15" s="4"/>
-      <c r="R15" s="67"/>
-      <c r="S15" s="68"/>
-      <c r="T15" s="68"/>
-      <c r="U15" s="68"/>
-      <c r="V15" s="68"/>
-      <c r="W15" s="68"/>
-      <c r="X15" s="68"/>
-      <c r="Y15" s="68"/>
-      <c r="Z15" s="69"/>
+      <c r="R15" s="77"/>
+      <c r="S15" s="78"/>
+      <c r="T15" s="78"/>
+      <c r="U15" s="78"/>
+      <c r="V15" s="78"/>
+      <c r="W15" s="78"/>
+      <c r="X15" s="78"/>
+      <c r="Y15" s="78"/>
+      <c r="Z15" s="98"/>
     </row>
     <row r="16" spans="2:26" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="21"/>
-      <c r="C16" s="83"/>
-      <c r="D16" s="84"/>
-      <c r="E16" s="84"/>
-      <c r="F16" s="84"/>
-      <c r="G16" s="85"/>
-      <c r="H16" s="83"/>
-      <c r="I16" s="84"/>
-      <c r="J16" s="84"/>
-      <c r="K16" s="85"/>
-      <c r="L16" s="18"/>
-      <c r="M16" s="18"/>
-      <c r="N16" s="18"/>
-      <c r="O16" s="130"/>
-      <c r="P16" s="70"/>
-      <c r="Q16" s="18"/>
-      <c r="Z16" s="15"/>
+      <c r="B16" s="123"/>
+      <c r="C16" s="125"/>
+      <c r="D16" s="126"/>
+      <c r="E16" s="126"/>
+      <c r="F16" s="126"/>
+      <c r="G16" s="127"/>
+      <c r="H16" s="125"/>
+      <c r="I16" s="126"/>
+      <c r="J16" s="126"/>
+      <c r="K16" s="127"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="17"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="99"/>
+      <c r="P16" s="100"/>
+      <c r="Q16" s="17"/>
+      <c r="Z16" s="14"/>
     </row>
     <row r="17" spans="2:26" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="8"/>
-      <c r="C17" s="45"/>
-      <c r="D17" s="46"/>
-      <c r="E17" s="46"/>
-      <c r="F17" s="46"/>
-      <c r="G17" s="47"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="46"/>
-      <c r="J17" s="46"/>
-      <c r="K17" s="47"/>
-      <c r="L17" s="19"/>
-      <c r="M17" s="20"/>
-      <c r="N17" s="20"/>
-      <c r="O17" s="63"/>
-      <c r="P17" s="64"/>
+      <c r="B17" s="124"/>
+      <c r="C17" s="128"/>
+      <c r="D17" s="129"/>
+      <c r="E17" s="129"/>
+      <c r="F17" s="129"/>
+      <c r="G17" s="130"/>
+      <c r="H17" s="128"/>
+      <c r="I17" s="129"/>
+      <c r="J17" s="129"/>
+      <c r="K17" s="130"/>
+      <c r="L17" s="18"/>
+      <c r="M17" s="19"/>
+      <c r="N17" s="19"/>
+      <c r="O17" s="95"/>
+      <c r="P17" s="96"/>
       <c r="Q17" s="5"/>
-      <c r="R17" s="59" t="s">
+      <c r="R17" s="91" t="s">
         <v>9</v>
       </c>
-      <c r="S17" s="14" t="s">
+      <c r="S17" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="T17" s="57" t="s">
+      <c r="T17" s="89" t="s">
         <v>11</v>
       </c>
-      <c r="U17" s="62"/>
-      <c r="V17" s="58"/>
-      <c r="W17" s="14" t="s">
+      <c r="U17" s="94"/>
+      <c r="V17" s="90"/>
+      <c r="W17" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="X17" s="13" t="s">
+      <c r="X17" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="Y17" s="57" t="s">
+      <c r="Y17" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="Z17" s="58"/>
+      <c r="Z17" s="90"/>
     </row>
     <row r="18" spans="2:26" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="92" t="s">
+      <c r="B18" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="93"/>
-      <c r="D18" s="93"/>
-      <c r="E18" s="94"/>
-      <c r="F18" s="98" t="s">
+      <c r="C18" s="46"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="G18" s="99"/>
-      <c r="H18" s="99"/>
-      <c r="I18" s="99"/>
-      <c r="J18" s="99"/>
-      <c r="K18" s="100"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="11"/>
-      <c r="O18" s="77"/>
-      <c r="P18" s="78"/>
-      <c r="Q18" s="12"/>
-      <c r="R18" s="60"/>
-      <c r="S18" s="31"/>
-      <c r="T18" s="33"/>
-      <c r="U18" s="34"/>
-      <c r="V18" s="35"/>
-      <c r="W18" s="31"/>
-      <c r="X18" s="31"/>
-      <c r="Y18" s="33"/>
-      <c r="Z18" s="35"/>
+      <c r="G18" s="52"/>
+      <c r="H18" s="52"/>
+      <c r="I18" s="52"/>
+      <c r="J18" s="52"/>
+      <c r="K18" s="53"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="103"/>
+      <c r="P18" s="104"/>
+      <c r="Q18" s="11"/>
+      <c r="R18" s="92"/>
+      <c r="S18" s="113"/>
+      <c r="T18" s="115"/>
+      <c r="U18" s="116"/>
+      <c r="V18" s="117"/>
+      <c r="W18" s="113"/>
+      <c r="X18" s="113"/>
+      <c r="Y18" s="115"/>
+      <c r="Z18" s="117"/>
     </row>
     <row r="19" spans="2:26" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="95"/>
-      <c r="C19" s="96"/>
-      <c r="D19" s="96"/>
-      <c r="E19" s="97"/>
-      <c r="F19" s="101" t="s">
+      <c r="B19" s="48"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="G19" s="102"/>
-      <c r="H19" s="102"/>
-      <c r="I19" s="102"/>
-      <c r="J19" s="102"/>
-      <c r="K19" s="103"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="12"/>
-      <c r="O19" s="79"/>
-      <c r="P19" s="80"/>
-      <c r="Q19" s="12"/>
-      <c r="R19" s="61"/>
-      <c r="S19" s="32"/>
-      <c r="T19" s="36"/>
-      <c r="U19" s="37"/>
-      <c r="V19" s="38"/>
-      <c r="W19" s="32"/>
-      <c r="X19" s="32"/>
-      <c r="Y19" s="36"/>
-      <c r="Z19" s="38"/>
+      <c r="G19" s="55"/>
+      <c r="H19" s="55"/>
+      <c r="I19" s="55"/>
+      <c r="J19" s="55"/>
+      <c r="K19" s="56"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="105"/>
+      <c r="P19" s="106"/>
+      <c r="Q19" s="11"/>
+      <c r="R19" s="93"/>
+      <c r="S19" s="114"/>
+      <c r="T19" s="118"/>
+      <c r="U19" s="119"/>
+      <c r="V19" s="120"/>
+      <c r="W19" s="114"/>
+      <c r="X19" s="114"/>
+      <c r="Y19" s="118"/>
+      <c r="Z19" s="120"/>
     </row>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="V8:Z8"/>
+    <mergeCell ref="V9:Z9"/>
+    <mergeCell ref="V10:Z10"/>
+    <mergeCell ref="B2:Z2"/>
+    <mergeCell ref="S18:S19"/>
+    <mergeCell ref="T18:V19"/>
+    <mergeCell ref="W18:W19"/>
+    <mergeCell ref="X18:X19"/>
+    <mergeCell ref="Y18:Z19"/>
+    <mergeCell ref="M7:U7"/>
+    <mergeCell ref="M8:U8"/>
+    <mergeCell ref="M9:U9"/>
+    <mergeCell ref="M10:U10"/>
+    <mergeCell ref="V7:Z7"/>
+    <mergeCell ref="H17:K17"/>
+    <mergeCell ref="P11:T11"/>
+    <mergeCell ref="P12:T12"/>
+    <mergeCell ref="U11:W11"/>
+    <mergeCell ref="U12:W12"/>
+    <mergeCell ref="X11:Z11"/>
+    <mergeCell ref="Y17:Z17"/>
+    <mergeCell ref="R17:R19"/>
+    <mergeCell ref="T17:V17"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="R14:Z15"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="O15:P15"/>
+    <mergeCell ref="L14:Q14"/>
+    <mergeCell ref="J11:O11"/>
+    <mergeCell ref="J12:O12"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H16:K16"/>
+    <mergeCell ref="H14:K15"/>
     <mergeCell ref="K7:L7"/>
     <mergeCell ref="K8:L8"/>
     <mergeCell ref="K9:L9"/>
@@ -2116,44 +2162,14 @@
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B8:F8"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H16:K16"/>
-    <mergeCell ref="H14:K15"/>
-    <mergeCell ref="P12:T12"/>
-    <mergeCell ref="U11:W11"/>
-    <mergeCell ref="U12:W12"/>
-    <mergeCell ref="X11:Z11"/>
-    <mergeCell ref="Y17:Z17"/>
-    <mergeCell ref="R17:R19"/>
-    <mergeCell ref="T17:V17"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="R14:Z15"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="O15:P15"/>
-    <mergeCell ref="L14:Q14"/>
-    <mergeCell ref="J11:O11"/>
-    <mergeCell ref="J12:O12"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="V8:Z8"/>
-    <mergeCell ref="V9:Z9"/>
-    <mergeCell ref="V10:Z10"/>
-    <mergeCell ref="B2:Z2"/>
-    <mergeCell ref="S18:S19"/>
-    <mergeCell ref="T18:V19"/>
-    <mergeCell ref="W18:W19"/>
-    <mergeCell ref="X18:X19"/>
-    <mergeCell ref="Y18:Z19"/>
-    <mergeCell ref="M7:U7"/>
-    <mergeCell ref="M8:U8"/>
-    <mergeCell ref="M9:U9"/>
-    <mergeCell ref="M10:U10"/>
-    <mergeCell ref="V7:Z7"/>
-    <mergeCell ref="H17:K17"/>
-    <mergeCell ref="P11:T11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="B11:C11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SupervisorMobility.API/DataAccess/Templates/Distribution Template.xlsx
+++ b/SupervisorMobility.API/DataAccess/Templates/Distribution Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ituriel\OneDrive\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/77304a4152b67e63/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98C057C8-2466-4837-B00B-6A48BCDFBF11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{8F0C5AC6-0745-4C74-BA90-9B4811E5F4D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64A359F1-671E-4DC6-99DC-68AAF6CAF6F0}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="18672" windowHeight="10320" xr2:uid="{443068A0-8518-4967-88E9-3028C04BF0EC}"/>
+    <workbookView xWindow="49365" yWindow="4110" windowWidth="31035" windowHeight="15300" xr2:uid="{443068A0-8518-4967-88E9-3028C04BF0EC}"/>
   </bookViews>
   <sheets>
     <sheet name="HOE DISTRIBUTION" sheetId="1" r:id="rId1"/>
@@ -848,46 +848,325 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -895,285 +1174,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1190,6 +1190,261 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>579536</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>207682</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC39673E-8A14-D479-37CD-4AAD927C643B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8467725" y="3590925"/>
+          <a:ext cx="398561" cy="426757"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>211105</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>199678</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6598284B-B8C4-1BBD-7F9A-C573AE45841F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9267825" y="3619500"/>
+          <a:ext cx="363505" cy="390178"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>617262</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>173387</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6BB853A-CB3B-2B7C-87A1-93A1FFDE136B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9953625" y="3609975"/>
+          <a:ext cx="483912" cy="373412"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>617641</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>187482</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{208CE789-E3AC-A325-2431-C7482BDDCB2B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10734675" y="3648075"/>
+          <a:ext cx="465241" cy="349407"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>430470</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>154270</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{670980EB-0BCF-7084-0468-9EF00535AE85}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11496675" y="3686175"/>
+          <a:ext cx="478095" cy="278095"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1563,33 +1818,33 @@
       <c r="Z1" s="3"/>
     </row>
     <row r="2" spans="2:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="112" t="s">
+      <c r="B2" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="112"/>
-      <c r="D2" s="112"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="112"/>
-      <c r="G2" s="112"/>
-      <c r="H2" s="112"/>
-      <c r="I2" s="112"/>
-      <c r="J2" s="112"/>
-      <c r="K2" s="112"/>
-      <c r="L2" s="112"/>
-      <c r="M2" s="112"/>
-      <c r="N2" s="112"/>
-      <c r="O2" s="112"/>
-      <c r="P2" s="112"/>
-      <c r="Q2" s="112"/>
-      <c r="R2" s="112"/>
-      <c r="S2" s="112"/>
-      <c r="T2" s="112"/>
-      <c r="U2" s="112"/>
-      <c r="V2" s="112"/>
-      <c r="W2" s="112"/>
-      <c r="X2" s="112"/>
-      <c r="Y2" s="112"/>
-      <c r="Z2" s="112"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="30"/>
+      <c r="S2" s="30"/>
+      <c r="T2" s="30"/>
+      <c r="U2" s="30"/>
+      <c r="V2" s="30"/>
+      <c r="W2" s="30"/>
+      <c r="X2" s="30"/>
+      <c r="Y2" s="30"/>
+      <c r="Z2" s="30"/>
     </row>
     <row r="3" spans="2:26" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="3"/>
@@ -1700,195 +1955,195 @@
       <c r="Z6" s="3"/>
     </row>
     <row r="7" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="68" t="s">
+      <c r="B7" s="118" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="69"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="70"/>
-      <c r="G7" s="62" t="s">
+      <c r="C7" s="119"/>
+      <c r="D7" s="119"/>
+      <c r="E7" s="119"/>
+      <c r="F7" s="120"/>
+      <c r="G7" s="110" t="s">
         <v>1</v>
       </c>
-      <c r="H7" s="63"/>
-      <c r="I7" s="63"/>
-      <c r="J7" s="63"/>
-      <c r="K7" s="38" t="s">
+      <c r="H7" s="111"/>
+      <c r="I7" s="111"/>
+      <c r="J7" s="111"/>
+      <c r="K7" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="L7" s="39"/>
-      <c r="M7" s="75" t="s">
+      <c r="L7" s="87"/>
+      <c r="M7" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="N7" s="75"/>
-      <c r="O7" s="75"/>
-      <c r="P7" s="75"/>
-      <c r="Q7" s="75"/>
-      <c r="R7" s="75"/>
-      <c r="S7" s="75"/>
-      <c r="T7" s="75"/>
-      <c r="U7" s="75"/>
-      <c r="V7" s="38" t="s">
+      <c r="N7" s="39"/>
+      <c r="O7" s="39"/>
+      <c r="P7" s="39"/>
+      <c r="Q7" s="39"/>
+      <c r="R7" s="39"/>
+      <c r="S7" s="39"/>
+      <c r="T7" s="39"/>
+      <c r="U7" s="39"/>
+      <c r="V7" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="W7" s="121"/>
-      <c r="X7" s="121"/>
-      <c r="Y7" s="121"/>
-      <c r="Z7" s="122"/>
+      <c r="W7" s="43"/>
+      <c r="X7" s="43"/>
+      <c r="Y7" s="43"/>
+      <c r="Z7" s="44"/>
     </row>
     <row r="8" spans="2:26" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B8" s="71"/>
-      <c r="C8" s="72"/>
-      <c r="D8" s="72"/>
-      <c r="E8" s="72"/>
-      <c r="F8" s="73"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="65"/>
-      <c r="I8" s="65"/>
-      <c r="J8" s="65"/>
-      <c r="K8" s="40"/>
-      <c r="L8" s="41"/>
-      <c r="M8" s="59"/>
-      <c r="N8" s="60"/>
-      <c r="O8" s="60"/>
-      <c r="P8" s="60"/>
-      <c r="Q8" s="60"/>
-      <c r="R8" s="60"/>
-      <c r="S8" s="60"/>
-      <c r="T8" s="60"/>
-      <c r="U8" s="61"/>
-      <c r="V8" s="107"/>
-      <c r="W8" s="107"/>
-      <c r="X8" s="107"/>
-      <c r="Y8" s="107"/>
-      <c r="Z8" s="108"/>
+      <c r="B8" s="121"/>
+      <c r="C8" s="122"/>
+      <c r="D8" s="122"/>
+      <c r="E8" s="122"/>
+      <c r="F8" s="123"/>
+      <c r="G8" s="112"/>
+      <c r="H8" s="113"/>
+      <c r="I8" s="113"/>
+      <c r="J8" s="113"/>
+      <c r="K8" s="88"/>
+      <c r="L8" s="89"/>
+      <c r="M8" s="40"/>
+      <c r="N8" s="26"/>
+      <c r="O8" s="26"/>
+      <c r="P8" s="26"/>
+      <c r="Q8" s="26"/>
+      <c r="R8" s="26"/>
+      <c r="S8" s="26"/>
+      <c r="T8" s="26"/>
+      <c r="U8" s="41"/>
+      <c r="V8" s="24"/>
+      <c r="W8" s="24"/>
+      <c r="X8" s="24"/>
+      <c r="Y8" s="24"/>
+      <c r="Z8" s="25"/>
     </row>
     <row r="9" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="127" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="30"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="32" t="s">
+      <c r="C9" s="108"/>
+      <c r="D9" s="109"/>
+      <c r="E9" s="107" t="s">
         <v>4</v>
       </c>
-      <c r="F9" s="31"/>
-      <c r="G9" s="32" t="s">
+      <c r="F9" s="109"/>
+      <c r="G9" s="107" t="s">
         <v>2</v>
       </c>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="31"/>
-      <c r="K9" s="42"/>
-      <c r="L9" s="43"/>
-      <c r="M9" s="59"/>
-      <c r="N9" s="60"/>
-      <c r="O9" s="60"/>
-      <c r="P9" s="60"/>
-      <c r="Q9" s="60"/>
-      <c r="R9" s="60"/>
-      <c r="S9" s="60"/>
-      <c r="T9" s="60"/>
-      <c r="U9" s="61"/>
-      <c r="V9" s="60"/>
-      <c r="W9" s="60"/>
-      <c r="X9" s="60"/>
-      <c r="Y9" s="60"/>
-      <c r="Z9" s="109"/>
+      <c r="H9" s="108"/>
+      <c r="I9" s="108"/>
+      <c r="J9" s="109"/>
+      <c r="K9" s="90"/>
+      <c r="L9" s="91"/>
+      <c r="M9" s="40"/>
+      <c r="N9" s="26"/>
+      <c r="O9" s="26"/>
+      <c r="P9" s="26"/>
+      <c r="Q9" s="26"/>
+      <c r="R9" s="26"/>
+      <c r="S9" s="26"/>
+      <c r="T9" s="26"/>
+      <c r="U9" s="41"/>
+      <c r="V9" s="26"/>
+      <c r="W9" s="26"/>
+      <c r="X9" s="26"/>
+      <c r="Y9" s="26"/>
+      <c r="Z9" s="27"/>
     </row>
     <row r="10" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B10" s="33"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="59"/>
-      <c r="H10" s="60"/>
-      <c r="I10" s="60"/>
-      <c r="J10" s="61"/>
-      <c r="K10" s="44"/>
-      <c r="L10" s="41"/>
-      <c r="M10" s="59"/>
-      <c r="N10" s="60"/>
-      <c r="O10" s="60"/>
-      <c r="P10" s="60"/>
-      <c r="Q10" s="60"/>
-      <c r="R10" s="60"/>
-      <c r="S10" s="60"/>
-      <c r="T10" s="60"/>
-      <c r="U10" s="61"/>
-      <c r="V10" s="110"/>
-      <c r="W10" s="111"/>
-      <c r="X10" s="60"/>
-      <c r="Y10" s="60"/>
-      <c r="Z10" s="109"/>
+      <c r="B10" s="128"/>
+      <c r="C10" s="72"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="129"/>
+      <c r="F10" s="73"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="41"/>
+      <c r="K10" s="92"/>
+      <c r="L10" s="89"/>
+      <c r="M10" s="40"/>
+      <c r="N10" s="26"/>
+      <c r="O10" s="26"/>
+      <c r="P10" s="26"/>
+      <c r="Q10" s="26"/>
+      <c r="R10" s="26"/>
+      <c r="S10" s="26"/>
+      <c r="T10" s="26"/>
+      <c r="U10" s="41"/>
+      <c r="V10" s="28"/>
+      <c r="W10" s="29"/>
+      <c r="X10" s="26"/>
+      <c r="Y10" s="26"/>
+      <c r="Z10" s="27"/>
     </row>
     <row r="11" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B11" s="37" t="s">
+      <c r="B11" s="130" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="26"/>
-      <c r="D11" s="24" t="s">
+      <c r="C11" s="125"/>
+      <c r="D11" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="25"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="66" t="s">
+      <c r="E11" s="77"/>
+      <c r="F11" s="125"/>
+      <c r="G11" s="114" t="s">
         <v>26</v>
       </c>
-      <c r="H11" s="67"/>
+      <c r="H11" s="115"/>
       <c r="I11" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="J11" s="24" t="s">
+      <c r="J11" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="K11" s="25"/>
-      <c r="L11" s="25"/>
-      <c r="M11" s="25"/>
-      <c r="N11" s="25"/>
-      <c r="O11" s="25"/>
-      <c r="P11" s="83" t="s">
+      <c r="K11" s="77"/>
+      <c r="L11" s="77"/>
+      <c r="M11" s="77"/>
+      <c r="N11" s="77"/>
+      <c r="O11" s="77"/>
+      <c r="P11" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="Q11" s="84"/>
-      <c r="R11" s="84"/>
-      <c r="S11" s="84"/>
-      <c r="T11" s="84"/>
-      <c r="U11" s="83" t="s">
+      <c r="Q11" s="49"/>
+      <c r="R11" s="49"/>
+      <c r="S11" s="49"/>
+      <c r="T11" s="49"/>
+      <c r="U11" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="V11" s="84"/>
-      <c r="W11" s="85"/>
-      <c r="X11" s="86" t="s">
+      <c r="V11" s="49"/>
+      <c r="W11" s="53"/>
+      <c r="X11" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="Y11" s="87"/>
-      <c r="Z11" s="88"/>
+      <c r="Y11" s="55"/>
+      <c r="Z11" s="56"/>
     </row>
     <row r="12" spans="2:26" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="22"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="23"/>
+      <c r="B12" s="124"/>
+      <c r="C12" s="117"/>
+      <c r="D12" s="116"/>
+      <c r="E12" s="126"/>
+      <c r="F12" s="117"/>
+      <c r="G12" s="116"/>
+      <c r="H12" s="117"/>
       <c r="I12" s="7"/>
-      <c r="J12" s="80"/>
-      <c r="K12" s="81"/>
-      <c r="L12" s="81"/>
-      <c r="M12" s="81"/>
-      <c r="N12" s="81"/>
-      <c r="O12" s="81"/>
-      <c r="P12" s="80"/>
-      <c r="Q12" s="81"/>
-      <c r="R12" s="81"/>
-      <c r="S12" s="81"/>
-      <c r="T12" s="82"/>
-      <c r="U12" s="80"/>
-      <c r="V12" s="81"/>
-      <c r="W12" s="82"/>
+      <c r="J12" s="50"/>
+      <c r="K12" s="51"/>
+      <c r="L12" s="51"/>
+      <c r="M12" s="51"/>
+      <c r="N12" s="51"/>
+      <c r="O12" s="51"/>
+      <c r="P12" s="50"/>
+      <c r="Q12" s="51"/>
+      <c r="R12" s="51"/>
+      <c r="S12" s="51"/>
+      <c r="T12" s="52"/>
+      <c r="U12" s="50"/>
+      <c r="V12" s="51"/>
+      <c r="W12" s="52"/>
       <c r="X12" s="20"/>
       <c r="Y12" s="6" t="s">
         <v>21</v>
@@ -1923,191 +2178,237 @@
       <c r="Z13" s="3"/>
     </row>
     <row r="14" spans="2:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="57" t="s">
+      <c r="B14" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="74" t="s">
+      <c r="C14" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="75"/>
-      <c r="E14" s="75"/>
-      <c r="F14" s="75"/>
-      <c r="G14" s="76"/>
-      <c r="H14" s="74" t="s">
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="82"/>
+      <c r="H14" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="I14" s="75"/>
-      <c r="J14" s="75"/>
-      <c r="K14" s="76"/>
-      <c r="L14" s="101" t="s">
+      <c r="I14" s="39"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="82"/>
+      <c r="L14" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="M14" s="102"/>
-      <c r="N14" s="102"/>
-      <c r="O14" s="102"/>
-      <c r="P14" s="102"/>
-      <c r="Q14" s="102"/>
-      <c r="R14" s="74" t="s">
+      <c r="M14" s="75"/>
+      <c r="N14" s="75"/>
+      <c r="O14" s="75"/>
+      <c r="P14" s="75"/>
+      <c r="Q14" s="75"/>
+      <c r="R14" s="65" t="s">
         <v>15</v>
       </c>
-      <c r="S14" s="75"/>
-      <c r="T14" s="75"/>
-      <c r="U14" s="75"/>
-      <c r="V14" s="75"/>
-      <c r="W14" s="75"/>
-      <c r="X14" s="75"/>
-      <c r="Y14" s="75"/>
-      <c r="Z14" s="97"/>
+      <c r="S14" s="39"/>
+      <c r="T14" s="39"/>
+      <c r="U14" s="39"/>
+      <c r="V14" s="39"/>
+      <c r="W14" s="39"/>
+      <c r="X14" s="39"/>
+      <c r="Y14" s="39"/>
+      <c r="Z14" s="66"/>
     </row>
     <row r="15" spans="2:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="58"/>
-      <c r="C15" s="77" t="s">
+      <c r="B15" s="106"/>
+      <c r="C15" s="67" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="78"/>
-      <c r="E15" s="78"/>
-      <c r="F15" s="78"/>
-      <c r="G15" s="79"/>
-      <c r="H15" s="77"/>
-      <c r="I15" s="78"/>
-      <c r="J15" s="78"/>
-      <c r="K15" s="79"/>
+      <c r="D15" s="68"/>
+      <c r="E15" s="68"/>
+      <c r="F15" s="68"/>
+      <c r="G15" s="83"/>
+      <c r="H15" s="67"/>
+      <c r="I15" s="68"/>
+      <c r="J15" s="68"/>
+      <c r="K15" s="83"/>
       <c r="L15" s="16"/>
       <c r="M15" s="16"/>
       <c r="N15" s="16"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="35"/>
+      <c r="O15" s="72"/>
+      <c r="P15" s="73"/>
       <c r="Q15" s="4"/>
-      <c r="R15" s="77"/>
-      <c r="S15" s="78"/>
-      <c r="T15" s="78"/>
-      <c r="U15" s="78"/>
-      <c r="V15" s="78"/>
-      <c r="W15" s="78"/>
-      <c r="X15" s="78"/>
-      <c r="Y15" s="78"/>
-      <c r="Z15" s="98"/>
+      <c r="R15" s="67"/>
+      <c r="S15" s="68"/>
+      <c r="T15" s="68"/>
+      <c r="U15" s="68"/>
+      <c r="V15" s="68"/>
+      <c r="W15" s="68"/>
+      <c r="X15" s="68"/>
+      <c r="Y15" s="68"/>
+      <c r="Z15" s="69"/>
     </row>
     <row r="16" spans="2:26" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="123"/>
-      <c r="C16" s="125"/>
-      <c r="D16" s="126"/>
-      <c r="E16" s="126"/>
-      <c r="F16" s="126"/>
-      <c r="G16" s="127"/>
-      <c r="H16" s="125"/>
-      <c r="I16" s="126"/>
-      <c r="J16" s="126"/>
-      <c r="K16" s="127"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="84"/>
+      <c r="D16" s="85"/>
+      <c r="E16" s="85"/>
+      <c r="F16" s="85"/>
+      <c r="G16" s="86"/>
+      <c r="H16" s="84"/>
+      <c r="I16" s="85"/>
+      <c r="J16" s="85"/>
+      <c r="K16" s="86"/>
       <c r="L16" s="17"/>
       <c r="M16" s="17"/>
       <c r="N16" s="17"/>
-      <c r="O16" s="99"/>
-      <c r="P16" s="100"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="71"/>
       <c r="Q16" s="17"/>
       <c r="Z16" s="14"/>
     </row>
     <row r="17" spans="2:26" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="124"/>
-      <c r="C17" s="128"/>
-      <c r="D17" s="129"/>
-      <c r="E17" s="129"/>
-      <c r="F17" s="129"/>
-      <c r="G17" s="130"/>
-      <c r="H17" s="128"/>
-      <c r="I17" s="129"/>
-      <c r="J17" s="129"/>
-      <c r="K17" s="130"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="45"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="46"/>
+      <c r="G17" s="47"/>
+      <c r="H17" s="45"/>
+      <c r="I17" s="46"/>
+      <c r="J17" s="46"/>
+      <c r="K17" s="47"/>
       <c r="L17" s="18"/>
       <c r="M17" s="19"/>
       <c r="N17" s="19"/>
-      <c r="O17" s="95"/>
-      <c r="P17" s="96"/>
+      <c r="O17" s="63"/>
+      <c r="P17" s="64"/>
       <c r="Q17" s="5"/>
-      <c r="R17" s="91" t="s">
+      <c r="R17" s="59" t="s">
         <v>9</v>
       </c>
       <c r="S17" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="T17" s="89" t="s">
+      <c r="T17" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="U17" s="94"/>
-      <c r="V17" s="90"/>
+      <c r="U17" s="62"/>
+      <c r="V17" s="58"/>
       <c r="W17" s="13" t="s">
         <v>12</v>
       </c>
       <c r="X17" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="Y17" s="89" t="s">
+      <c r="Y17" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="Z17" s="90"/>
+      <c r="Z17" s="58"/>
     </row>
     <row r="18" spans="2:26" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="45" t="s">
+      <c r="B18" s="93" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="46"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="51" t="s">
+      <c r="C18" s="94"/>
+      <c r="D18" s="94"/>
+      <c r="E18" s="95"/>
+      <c r="F18" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="G18" s="52"/>
-      <c r="H18" s="52"/>
-      <c r="I18" s="52"/>
-      <c r="J18" s="52"/>
-      <c r="K18" s="53"/>
+      <c r="G18" s="100"/>
+      <c r="H18" s="100"/>
+      <c r="I18" s="100"/>
+      <c r="J18" s="100"/>
+      <c r="K18" s="101"/>
       <c r="L18" s="8"/>
       <c r="M18" s="8"/>
       <c r="N18" s="10"/>
-      <c r="O18" s="103"/>
-      <c r="P18" s="104"/>
+      <c r="O18" s="78"/>
+      <c r="P18" s="79"/>
       <c r="Q18" s="11"/>
-      <c r="R18" s="92"/>
-      <c r="S18" s="113"/>
-      <c r="T18" s="115"/>
-      <c r="U18" s="116"/>
-      <c r="V18" s="117"/>
-      <c r="W18" s="113"/>
-      <c r="X18" s="113"/>
-      <c r="Y18" s="115"/>
-      <c r="Z18" s="117"/>
+      <c r="R18" s="60"/>
+      <c r="S18" s="31"/>
+      <c r="T18" s="33"/>
+      <c r="U18" s="34"/>
+      <c r="V18" s="35"/>
+      <c r="W18" s="31"/>
+      <c r="X18" s="31"/>
+      <c r="Y18" s="33"/>
+      <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="2:26" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="48"/>
-      <c r="C19" s="49"/>
-      <c r="D19" s="49"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="54" t="s">
+      <c r="B19" s="96"/>
+      <c r="C19" s="97"/>
+      <c r="D19" s="97"/>
+      <c r="E19" s="98"/>
+      <c r="F19" s="102" t="s">
         <v>8</v>
       </c>
-      <c r="G19" s="55"/>
-      <c r="H19" s="55"/>
-      <c r="I19" s="55"/>
-      <c r="J19" s="55"/>
-      <c r="K19" s="56"/>
+      <c r="G19" s="103"/>
+      <c r="H19" s="103"/>
+      <c r="I19" s="103"/>
+      <c r="J19" s="103"/>
+      <c r="K19" s="104"/>
       <c r="L19" s="8"/>
       <c r="M19" s="9"/>
       <c r="N19" s="11"/>
-      <c r="O19" s="105"/>
-      <c r="P19" s="106"/>
+      <c r="O19" s="80"/>
+      <c r="P19" s="81"/>
       <c r="Q19" s="11"/>
-      <c r="R19" s="93"/>
-      <c r="S19" s="114"/>
-      <c r="T19" s="118"/>
-      <c r="U19" s="119"/>
-      <c r="V19" s="120"/>
-      <c r="W19" s="114"/>
-      <c r="X19" s="114"/>
-      <c r="Y19" s="118"/>
-      <c r="Z19" s="120"/>
+      <c r="R19" s="61"/>
+      <c r="S19" s="32"/>
+      <c r="T19" s="36"/>
+      <c r="U19" s="37"/>
+      <c r="V19" s="38"/>
+      <c r="W19" s="32"/>
+      <c r="X19" s="32"/>
+      <c r="Y19" s="36"/>
+      <c r="Z19" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="62">
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="B18:E19"/>
+    <mergeCell ref="F18:K18"/>
+    <mergeCell ref="F19:K19"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="G10:J10"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H16:K16"/>
+    <mergeCell ref="H14:K15"/>
+    <mergeCell ref="P12:T12"/>
+    <mergeCell ref="U11:W11"/>
+    <mergeCell ref="U12:W12"/>
+    <mergeCell ref="X11:Z11"/>
+    <mergeCell ref="Y17:Z17"/>
+    <mergeCell ref="R17:R19"/>
+    <mergeCell ref="T17:V17"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="R14:Z15"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="O15:P15"/>
+    <mergeCell ref="L14:Q14"/>
+    <mergeCell ref="J11:O11"/>
+    <mergeCell ref="J12:O12"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="O19:P19"/>
     <mergeCell ref="V8:Z8"/>
     <mergeCell ref="V9:Z9"/>
     <mergeCell ref="V10:Z10"/>
@@ -2124,53 +2425,8 @@
     <mergeCell ref="V7:Z7"/>
     <mergeCell ref="H17:K17"/>
     <mergeCell ref="P11:T11"/>
-    <mergeCell ref="P12:T12"/>
-    <mergeCell ref="U11:W11"/>
-    <mergeCell ref="U12:W12"/>
-    <mergeCell ref="X11:Z11"/>
-    <mergeCell ref="Y17:Z17"/>
-    <mergeCell ref="R17:R19"/>
-    <mergeCell ref="T17:V17"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="R14:Z15"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="O15:P15"/>
-    <mergeCell ref="L14:Q14"/>
-    <mergeCell ref="J11:O11"/>
-    <mergeCell ref="J12:O12"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H16:K16"/>
-    <mergeCell ref="H14:K15"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="B18:E19"/>
-    <mergeCell ref="F18:K18"/>
-    <mergeCell ref="F19:K19"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="G10:J10"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="G7:J7"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="B11:C11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/SupervisorMobility.API/DataAccess/Templates/Distribution Template.xlsx
+++ b/SupervisorMobility.API/DataAccess/Templates/Distribution Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/77304a4152b67e63/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\job\Supervisor app\Server\SupervisorMobility.API\DataAccess\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{8F0C5AC6-0745-4C74-BA90-9B4811E5F4D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64A359F1-671E-4DC6-99DC-68AAF6CAF6F0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF4FC2A9-88A8-4836-AB07-9ACDD4AE4EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="49365" yWindow="4110" windowWidth="31035" windowHeight="15300" xr2:uid="{443068A0-8518-4967-88E9-3028C04BF0EC}"/>
+    <workbookView xWindow="47205" yWindow="5445" windowWidth="19890" windowHeight="12300" xr2:uid="{443068A0-8518-4967-88E9-3028C04BF0EC}"/>
   </bookViews>
   <sheets>
     <sheet name="HOE DISTRIBUTION" sheetId="1" r:id="rId1"/>
@@ -854,68 +854,188 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -926,21 +1046,21 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -977,18 +1097,9 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -998,24 +1109,12 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1028,152 +1127,53 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1203,7 +1203,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>579536</xdr:colOff>
+      <xdr:colOff>590966</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>207682</xdr:rowOff>
     </xdr:to>
@@ -1255,7 +1255,7 @@
       <xdr:col>21</xdr:col>
       <xdr:colOff>211105</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>199678</xdr:rowOff>
+      <xdr:rowOff>211108</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1303,7 +1303,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>617262</xdr:colOff>
+      <xdr:colOff>628692</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>173387</xdr:rowOff>
     </xdr:to>
@@ -1353,7 +1353,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>617641</xdr:colOff>
+      <xdr:colOff>629071</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>187482</xdr:rowOff>
     </xdr:to>
@@ -1397,15 +1397,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>24</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
+      <xdr:colOff>131445</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>228600</xdr:rowOff>
+      <xdr:rowOff>211454</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>430470</xdr:colOff>
+      <xdr:colOff>416182</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>154270</xdr:rowOff>
+      <xdr:rowOff>137981</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1434,8 +1434,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11496675" y="3686175"/>
-          <a:ext cx="478095" cy="278095"/>
+          <a:off x="11475720" y="3669029"/>
+          <a:ext cx="484762" cy="278952"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1818,33 +1818,33 @@
       <c r="Z1" s="3"/>
     </row>
     <row r="2" spans="2:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="120" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
-      <c r="T2" s="30"/>
-      <c r="U2" s="30"/>
-      <c r="V2" s="30"/>
-      <c r="W2" s="30"/>
-      <c r="X2" s="30"/>
-      <c r="Y2" s="30"/>
-      <c r="Z2" s="30"/>
+      <c r="C2" s="120"/>
+      <c r="D2" s="120"/>
+      <c r="E2" s="120"/>
+      <c r="F2" s="120"/>
+      <c r="G2" s="120"/>
+      <c r="H2" s="120"/>
+      <c r="I2" s="120"/>
+      <c r="J2" s="120"/>
+      <c r="K2" s="120"/>
+      <c r="L2" s="120"/>
+      <c r="M2" s="120"/>
+      <c r="N2" s="120"/>
+      <c r="O2" s="120"/>
+      <c r="P2" s="120"/>
+      <c r="Q2" s="120"/>
+      <c r="R2" s="120"/>
+      <c r="S2" s="120"/>
+      <c r="T2" s="120"/>
+      <c r="U2" s="120"/>
+      <c r="V2" s="120"/>
+      <c r="W2" s="120"/>
+      <c r="X2" s="120"/>
+      <c r="Y2" s="120"/>
+      <c r="Z2" s="120"/>
     </row>
     <row r="3" spans="2:26" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="3"/>
@@ -1955,195 +1955,195 @@
       <c r="Z6" s="3"/>
     </row>
     <row r="7" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="118" t="s">
+      <c r="B7" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="119"/>
-      <c r="D7" s="119"/>
-      <c r="E7" s="119"/>
-      <c r="F7" s="120"/>
-      <c r="G7" s="110" t="s">
+      <c r="C7" s="71"/>
+      <c r="D7" s="71"/>
+      <c r="E7" s="71"/>
+      <c r="F7" s="72"/>
+      <c r="G7" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="42" t="s">
+      <c r="H7" s="65"/>
+      <c r="I7" s="65"/>
+      <c r="J7" s="65"/>
+      <c r="K7" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="L7" s="87"/>
-      <c r="M7" s="39" t="s">
+      <c r="L7" s="41"/>
+      <c r="M7" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="N7" s="39"/>
-      <c r="O7" s="39"/>
-      <c r="P7" s="39"/>
-      <c r="Q7" s="39"/>
-      <c r="R7" s="39"/>
-      <c r="S7" s="39"/>
-      <c r="T7" s="39"/>
-      <c r="U7" s="39"/>
-      <c r="V7" s="42" t="s">
+      <c r="N7" s="77"/>
+      <c r="O7" s="77"/>
+      <c r="P7" s="77"/>
+      <c r="Q7" s="77"/>
+      <c r="R7" s="77"/>
+      <c r="S7" s="77"/>
+      <c r="T7" s="77"/>
+      <c r="U7" s="77"/>
+      <c r="V7" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="W7" s="43"/>
-      <c r="X7" s="43"/>
-      <c r="Y7" s="43"/>
-      <c r="Z7" s="44"/>
+      <c r="W7" s="129"/>
+      <c r="X7" s="129"/>
+      <c r="Y7" s="129"/>
+      <c r="Z7" s="130"/>
     </row>
     <row r="8" spans="2:26" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B8" s="121"/>
-      <c r="C8" s="122"/>
-      <c r="D8" s="122"/>
-      <c r="E8" s="122"/>
-      <c r="F8" s="123"/>
-      <c r="G8" s="112"/>
-      <c r="H8" s="113"/>
-      <c r="I8" s="113"/>
-      <c r="J8" s="113"/>
-      <c r="K8" s="88"/>
-      <c r="L8" s="89"/>
-      <c r="M8" s="40"/>
-      <c r="N8" s="26"/>
-      <c r="O8" s="26"/>
-      <c r="P8" s="26"/>
-      <c r="Q8" s="26"/>
-      <c r="R8" s="26"/>
-      <c r="S8" s="26"/>
-      <c r="T8" s="26"/>
-      <c r="U8" s="41"/>
-      <c r="V8" s="24"/>
-      <c r="W8" s="24"/>
-      <c r="X8" s="24"/>
-      <c r="Y8" s="24"/>
-      <c r="Z8" s="25"/>
+      <c r="B8" s="73"/>
+      <c r="C8" s="74"/>
+      <c r="D8" s="74"/>
+      <c r="E8" s="74"/>
+      <c r="F8" s="75"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="67"/>
+      <c r="J8" s="67"/>
+      <c r="K8" s="42"/>
+      <c r="L8" s="43"/>
+      <c r="M8" s="61"/>
+      <c r="N8" s="62"/>
+      <c r="O8" s="62"/>
+      <c r="P8" s="62"/>
+      <c r="Q8" s="62"/>
+      <c r="R8" s="62"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="62"/>
+      <c r="U8" s="63"/>
+      <c r="V8" s="115"/>
+      <c r="W8" s="115"/>
+      <c r="X8" s="115"/>
+      <c r="Y8" s="115"/>
+      <c r="Z8" s="116"/>
     </row>
     <row r="9" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B9" s="127" t="s">
+      <c r="B9" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="108"/>
-      <c r="D9" s="109"/>
-      <c r="E9" s="107" t="s">
+      <c r="C9" s="32"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="F9" s="109"/>
-      <c r="G9" s="107" t="s">
+      <c r="F9" s="33"/>
+      <c r="G9" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="H9" s="108"/>
-      <c r="I9" s="108"/>
-      <c r="J9" s="109"/>
-      <c r="K9" s="90"/>
-      <c r="L9" s="91"/>
-      <c r="M9" s="40"/>
-      <c r="N9" s="26"/>
-      <c r="O9" s="26"/>
-      <c r="P9" s="26"/>
-      <c r="Q9" s="26"/>
-      <c r="R9" s="26"/>
-      <c r="S9" s="26"/>
-      <c r="T9" s="26"/>
-      <c r="U9" s="41"/>
-      <c r="V9" s="26"/>
-      <c r="W9" s="26"/>
-      <c r="X9" s="26"/>
-      <c r="Y9" s="26"/>
-      <c r="Z9" s="27"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="33"/>
+      <c r="K9" s="44"/>
+      <c r="L9" s="45"/>
+      <c r="M9" s="61"/>
+      <c r="N9" s="62"/>
+      <c r="O9" s="62"/>
+      <c r="P9" s="62"/>
+      <c r="Q9" s="62"/>
+      <c r="R9" s="62"/>
+      <c r="S9" s="62"/>
+      <c r="T9" s="62"/>
+      <c r="U9" s="63"/>
+      <c r="V9" s="62"/>
+      <c r="W9" s="62"/>
+      <c r="X9" s="62"/>
+      <c r="Y9" s="62"/>
+      <c r="Z9" s="117"/>
     </row>
     <row r="10" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B10" s="128"/>
-      <c r="C10" s="72"/>
-      <c r="D10" s="73"/>
-      <c r="E10" s="129"/>
-      <c r="F10" s="73"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="41"/>
-      <c r="K10" s="92"/>
-      <c r="L10" s="89"/>
-      <c r="M10" s="40"/>
-      <c r="N10" s="26"/>
-      <c r="O10" s="26"/>
-      <c r="P10" s="26"/>
-      <c r="Q10" s="26"/>
-      <c r="R10" s="26"/>
-      <c r="S10" s="26"/>
-      <c r="T10" s="26"/>
-      <c r="U10" s="41"/>
-      <c r="V10" s="28"/>
-      <c r="W10" s="29"/>
-      <c r="X10" s="26"/>
-      <c r="Y10" s="26"/>
-      <c r="Z10" s="27"/>
+      <c r="B10" s="35"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="37"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="62"/>
+      <c r="I10" s="62"/>
+      <c r="J10" s="63"/>
+      <c r="K10" s="46"/>
+      <c r="L10" s="43"/>
+      <c r="M10" s="61"/>
+      <c r="N10" s="62"/>
+      <c r="O10" s="62"/>
+      <c r="P10" s="62"/>
+      <c r="Q10" s="62"/>
+      <c r="R10" s="62"/>
+      <c r="S10" s="62"/>
+      <c r="T10" s="62"/>
+      <c r="U10" s="63"/>
+      <c r="V10" s="118"/>
+      <c r="W10" s="119"/>
+      <c r="X10" s="62"/>
+      <c r="Y10" s="62"/>
+      <c r="Z10" s="117"/>
     </row>
     <row r="11" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B11" s="130" t="s">
+      <c r="B11" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="125"/>
-      <c r="D11" s="76" t="s">
+      <c r="C11" s="28"/>
+      <c r="D11" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="77"/>
-      <c r="F11" s="125"/>
-      <c r="G11" s="114" t="s">
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="H11" s="115"/>
+      <c r="H11" s="69"/>
       <c r="I11" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="J11" s="76" t="s">
+      <c r="J11" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="K11" s="77"/>
-      <c r="L11" s="77"/>
-      <c r="M11" s="77"/>
-      <c r="N11" s="77"/>
-      <c r="O11" s="77"/>
-      <c r="P11" s="48" t="s">
+      <c r="K11" s="27"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="27"/>
+      <c r="P11" s="91" t="s">
         <v>29</v>
       </c>
-      <c r="Q11" s="49"/>
-      <c r="R11" s="49"/>
-      <c r="S11" s="49"/>
-      <c r="T11" s="49"/>
-      <c r="U11" s="48" t="s">
+      <c r="Q11" s="92"/>
+      <c r="R11" s="92"/>
+      <c r="S11" s="92"/>
+      <c r="T11" s="92"/>
+      <c r="U11" s="91" t="s">
         <v>30</v>
       </c>
-      <c r="V11" s="49"/>
-      <c r="W11" s="53"/>
-      <c r="X11" s="54" t="s">
+      <c r="V11" s="92"/>
+      <c r="W11" s="93"/>
+      <c r="X11" s="94" t="s">
         <v>31</v>
       </c>
-      <c r="Y11" s="55"/>
-      <c r="Z11" s="56"/>
+      <c r="Y11" s="95"/>
+      <c r="Z11" s="96"/>
     </row>
     <row r="12" spans="2:26" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="124"/>
-      <c r="C12" s="117"/>
-      <c r="D12" s="116"/>
-      <c r="E12" s="126"/>
-      <c r="F12" s="117"/>
-      <c r="G12" s="116"/>
-      <c r="H12" s="117"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="25"/>
       <c r="I12" s="7"/>
-      <c r="J12" s="50"/>
-      <c r="K12" s="51"/>
-      <c r="L12" s="51"/>
-      <c r="M12" s="51"/>
-      <c r="N12" s="51"/>
-      <c r="O12" s="51"/>
-      <c r="P12" s="50"/>
-      <c r="Q12" s="51"/>
-      <c r="R12" s="51"/>
-      <c r="S12" s="51"/>
-      <c r="T12" s="52"/>
-      <c r="U12" s="50"/>
-      <c r="V12" s="51"/>
-      <c r="W12" s="52"/>
+      <c r="J12" s="88"/>
+      <c r="K12" s="89"/>
+      <c r="L12" s="89"/>
+      <c r="M12" s="89"/>
+      <c r="N12" s="89"/>
+      <c r="O12" s="89"/>
+      <c r="P12" s="88"/>
+      <c r="Q12" s="89"/>
+      <c r="R12" s="89"/>
+      <c r="S12" s="89"/>
+      <c r="T12" s="90"/>
+      <c r="U12" s="88"/>
+      <c r="V12" s="89"/>
+      <c r="W12" s="90"/>
       <c r="X12" s="20"/>
       <c r="Y12" s="6" t="s">
         <v>21</v>
@@ -2178,199 +2178,229 @@
       <c r="Z13" s="3"/>
     </row>
     <row r="14" spans="2:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="105" t="s">
+      <c r="B14" s="59" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="65" t="s">
+      <c r="C14" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="82"/>
-      <c r="H14" s="65" t="s">
+      <c r="D14" s="77"/>
+      <c r="E14" s="77"/>
+      <c r="F14" s="77"/>
+      <c r="G14" s="78"/>
+      <c r="H14" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="I14" s="39"/>
-      <c r="J14" s="39"/>
-      <c r="K14" s="82"/>
-      <c r="L14" s="74" t="s">
+      <c r="I14" s="77"/>
+      <c r="J14" s="77"/>
+      <c r="K14" s="78"/>
+      <c r="L14" s="109" t="s">
         <v>16</v>
       </c>
-      <c r="M14" s="75"/>
-      <c r="N14" s="75"/>
-      <c r="O14" s="75"/>
-      <c r="P14" s="75"/>
-      <c r="Q14" s="75"/>
-      <c r="R14" s="65" t="s">
+      <c r="M14" s="110"/>
+      <c r="N14" s="110"/>
+      <c r="O14" s="110"/>
+      <c r="P14" s="110"/>
+      <c r="Q14" s="110"/>
+      <c r="R14" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="S14" s="39"/>
-      <c r="T14" s="39"/>
-      <c r="U14" s="39"/>
-      <c r="V14" s="39"/>
-      <c r="W14" s="39"/>
-      <c r="X14" s="39"/>
-      <c r="Y14" s="39"/>
-      <c r="Z14" s="66"/>
+      <c r="S14" s="77"/>
+      <c r="T14" s="77"/>
+      <c r="U14" s="77"/>
+      <c r="V14" s="77"/>
+      <c r="W14" s="77"/>
+      <c r="X14" s="77"/>
+      <c r="Y14" s="77"/>
+      <c r="Z14" s="105"/>
     </row>
     <row r="15" spans="2:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="106"/>
-      <c r="C15" s="67" t="s">
+      <c r="B15" s="60"/>
+      <c r="C15" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="68"/>
-      <c r="E15" s="68"/>
-      <c r="F15" s="68"/>
-      <c r="G15" s="83"/>
-      <c r="H15" s="67"/>
-      <c r="I15" s="68"/>
-      <c r="J15" s="68"/>
-      <c r="K15" s="83"/>
+      <c r="D15" s="80"/>
+      <c r="E15" s="80"/>
+      <c r="F15" s="80"/>
+      <c r="G15" s="81"/>
+      <c r="H15" s="79"/>
+      <c r="I15" s="80"/>
+      <c r="J15" s="80"/>
+      <c r="K15" s="81"/>
       <c r="L15" s="16"/>
       <c r="M15" s="16"/>
       <c r="N15" s="16"/>
-      <c r="O15" s="72"/>
-      <c r="P15" s="73"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="37"/>
       <c r="Q15" s="4"/>
-      <c r="R15" s="67"/>
-      <c r="S15" s="68"/>
-      <c r="T15" s="68"/>
-      <c r="U15" s="68"/>
-      <c r="V15" s="68"/>
-      <c r="W15" s="68"/>
-      <c r="X15" s="68"/>
-      <c r="Y15" s="68"/>
-      <c r="Z15" s="69"/>
+      <c r="R15" s="79"/>
+      <c r="S15" s="80"/>
+      <c r="T15" s="80"/>
+      <c r="U15" s="80"/>
+      <c r="V15" s="80"/>
+      <c r="W15" s="80"/>
+      <c r="X15" s="80"/>
+      <c r="Y15" s="80"/>
+      <c r="Z15" s="106"/>
     </row>
     <row r="16" spans="2:26" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="22"/>
-      <c r="C16" s="84"/>
-      <c r="D16" s="85"/>
-      <c r="E16" s="85"/>
-      <c r="F16" s="85"/>
-      <c r="G16" s="86"/>
-      <c r="H16" s="84"/>
-      <c r="I16" s="85"/>
-      <c r="J16" s="85"/>
-      <c r="K16" s="86"/>
+      <c r="C16" s="82"/>
+      <c r="D16" s="83"/>
+      <c r="E16" s="83"/>
+      <c r="F16" s="83"/>
+      <c r="G16" s="84"/>
+      <c r="H16" s="82"/>
+      <c r="I16" s="83"/>
+      <c r="J16" s="83"/>
+      <c r="K16" s="84"/>
       <c r="L16" s="17"/>
       <c r="M16" s="17"/>
       <c r="N16" s="17"/>
-      <c r="O16" s="70"/>
-      <c r="P16" s="71"/>
+      <c r="O16" s="107"/>
+      <c r="P16" s="108"/>
       <c r="Q16" s="17"/>
       <c r="Z16" s="14"/>
     </row>
     <row r="17" spans="2:26" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="23"/>
-      <c r="C17" s="45"/>
-      <c r="D17" s="46"/>
-      <c r="E17" s="46"/>
-      <c r="F17" s="46"/>
-      <c r="G17" s="47"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="46"/>
-      <c r="J17" s="46"/>
-      <c r="K17" s="47"/>
+      <c r="C17" s="85"/>
+      <c r="D17" s="86"/>
+      <c r="E17" s="86"/>
+      <c r="F17" s="86"/>
+      <c r="G17" s="87"/>
+      <c r="H17" s="85"/>
+      <c r="I17" s="86"/>
+      <c r="J17" s="86"/>
+      <c r="K17" s="87"/>
       <c r="L17" s="18"/>
       <c r="M17" s="19"/>
       <c r="N17" s="19"/>
-      <c r="O17" s="63"/>
-      <c r="P17" s="64"/>
+      <c r="O17" s="103"/>
+      <c r="P17" s="104"/>
       <c r="Q17" s="5"/>
-      <c r="R17" s="59" t="s">
+      <c r="R17" s="99" t="s">
         <v>9</v>
       </c>
       <c r="S17" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="T17" s="57" t="s">
+      <c r="T17" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="U17" s="62"/>
-      <c r="V17" s="58"/>
+      <c r="U17" s="102"/>
+      <c r="V17" s="98"/>
       <c r="W17" s="13" t="s">
         <v>12</v>
       </c>
       <c r="X17" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="Y17" s="57" t="s">
+      <c r="Y17" s="97" t="s">
         <v>14</v>
       </c>
-      <c r="Z17" s="58"/>
+      <c r="Z17" s="98"/>
     </row>
     <row r="18" spans="2:26" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="93" t="s">
+      <c r="B18" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="94"/>
-      <c r="D18" s="94"/>
-      <c r="E18" s="95"/>
-      <c r="F18" s="99" t="s">
+      <c r="C18" s="48"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="G18" s="100"/>
-      <c r="H18" s="100"/>
-      <c r="I18" s="100"/>
-      <c r="J18" s="100"/>
-      <c r="K18" s="101"/>
+      <c r="G18" s="54"/>
+      <c r="H18" s="54"/>
+      <c r="I18" s="54"/>
+      <c r="J18" s="54"/>
+      <c r="K18" s="55"/>
       <c r="L18" s="8"/>
       <c r="M18" s="8"/>
       <c r="N18" s="10"/>
-      <c r="O18" s="78"/>
-      <c r="P18" s="79"/>
+      <c r="O18" s="111"/>
+      <c r="P18" s="112"/>
       <c r="Q18" s="11"/>
-      <c r="R18" s="60"/>
-      <c r="S18" s="31"/>
-      <c r="T18" s="33"/>
-      <c r="U18" s="34"/>
-      <c r="V18" s="35"/>
-      <c r="W18" s="31"/>
-      <c r="X18" s="31"/>
-      <c r="Y18" s="33"/>
-      <c r="Z18" s="35"/>
+      <c r="R18" s="100"/>
+      <c r="S18" s="121"/>
+      <c r="T18" s="123"/>
+      <c r="U18" s="124"/>
+      <c r="V18" s="125"/>
+      <c r="W18" s="121"/>
+      <c r="X18" s="121"/>
+      <c r="Y18" s="123"/>
+      <c r="Z18" s="125"/>
     </row>
     <row r="19" spans="2:26" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="96"/>
-      <c r="C19" s="97"/>
-      <c r="D19" s="97"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="102" t="s">
+      <c r="B19" s="50"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="G19" s="103"/>
-      <c r="H19" s="103"/>
-      <c r="I19" s="103"/>
-      <c r="J19" s="103"/>
-      <c r="K19" s="104"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="57"/>
+      <c r="K19" s="58"/>
       <c r="L19" s="8"/>
       <c r="M19" s="9"/>
       <c r="N19" s="11"/>
-      <c r="O19" s="80"/>
-      <c r="P19" s="81"/>
+      <c r="O19" s="113"/>
+      <c r="P19" s="114"/>
       <c r="Q19" s="11"/>
-      <c r="R19" s="61"/>
-      <c r="S19" s="32"/>
-      <c r="T19" s="36"/>
-      <c r="U19" s="37"/>
-      <c r="V19" s="38"/>
-      <c r="W19" s="32"/>
-      <c r="X19" s="32"/>
-      <c r="Y19" s="36"/>
-      <c r="Z19" s="38"/>
+      <c r="R19" s="101"/>
+      <c r="S19" s="122"/>
+      <c r="T19" s="126"/>
+      <c r="U19" s="127"/>
+      <c r="V19" s="128"/>
+      <c r="W19" s="122"/>
+      <c r="X19" s="122"/>
+      <c r="Y19" s="126"/>
+      <c r="Z19" s="128"/>
     </row>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="V8:Z8"/>
+    <mergeCell ref="V9:Z9"/>
+    <mergeCell ref="V10:Z10"/>
+    <mergeCell ref="B2:Z2"/>
+    <mergeCell ref="S18:S19"/>
+    <mergeCell ref="T18:V19"/>
+    <mergeCell ref="W18:W19"/>
+    <mergeCell ref="X18:X19"/>
+    <mergeCell ref="Y18:Z19"/>
+    <mergeCell ref="M7:U7"/>
+    <mergeCell ref="M8:U8"/>
+    <mergeCell ref="M9:U9"/>
+    <mergeCell ref="M10:U10"/>
+    <mergeCell ref="V7:Z7"/>
+    <mergeCell ref="H17:K17"/>
+    <mergeCell ref="P11:T11"/>
+    <mergeCell ref="P12:T12"/>
+    <mergeCell ref="U11:W11"/>
+    <mergeCell ref="U12:W12"/>
+    <mergeCell ref="X11:Z11"/>
+    <mergeCell ref="Y17:Z17"/>
+    <mergeCell ref="R17:R19"/>
+    <mergeCell ref="T17:V17"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="R14:Z15"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="O15:P15"/>
+    <mergeCell ref="L14:Q14"/>
+    <mergeCell ref="J11:O11"/>
+    <mergeCell ref="J12:O12"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H16:K16"/>
+    <mergeCell ref="H14:K15"/>
     <mergeCell ref="K7:L7"/>
     <mergeCell ref="K8:L8"/>
     <mergeCell ref="K9:L9"/>
@@ -2387,44 +2417,14 @@
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B8:F8"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H16:K16"/>
-    <mergeCell ref="H14:K15"/>
-    <mergeCell ref="P12:T12"/>
-    <mergeCell ref="U11:W11"/>
-    <mergeCell ref="U12:W12"/>
-    <mergeCell ref="X11:Z11"/>
-    <mergeCell ref="Y17:Z17"/>
-    <mergeCell ref="R17:R19"/>
-    <mergeCell ref="T17:V17"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="R14:Z15"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="O15:P15"/>
-    <mergeCell ref="L14:Q14"/>
-    <mergeCell ref="J11:O11"/>
-    <mergeCell ref="J12:O12"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="V8:Z8"/>
-    <mergeCell ref="V9:Z9"/>
-    <mergeCell ref="V10:Z10"/>
-    <mergeCell ref="B2:Z2"/>
-    <mergeCell ref="S18:S19"/>
-    <mergeCell ref="T18:V19"/>
-    <mergeCell ref="W18:W19"/>
-    <mergeCell ref="X18:X19"/>
-    <mergeCell ref="Y18:Z19"/>
-    <mergeCell ref="M7:U7"/>
-    <mergeCell ref="M8:U8"/>
-    <mergeCell ref="M9:U9"/>
-    <mergeCell ref="M10:U10"/>
-    <mergeCell ref="V7:Z7"/>
-    <mergeCell ref="H17:K17"/>
-    <mergeCell ref="P11:T11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="B11:C11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/SupervisorMobility.API/DataAccess/Templates/Distribution Template.xlsx
+++ b/SupervisorMobility.API/DataAccess/Templates/Distribution Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\job\Supervisor app\Server\SupervisorMobility.API\DataAccess\Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carlo\source\repos\SupervisorMobility.API\SupervisorMobility.API\DataAccess\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF4FC2A9-88A8-4836-AB07-9ACDD4AE4EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C40FB0-5E7C-4DCD-A890-3A34B5805290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="47205" yWindow="5445" windowWidth="19890" windowHeight="12300" xr2:uid="{443068A0-8518-4967-88E9-3028C04BF0EC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{443068A0-8518-4967-88E9-3028C04BF0EC}"/>
   </bookViews>
   <sheets>
     <sheet name="HOE DISTRIBUTION" sheetId="1" r:id="rId1"/>
@@ -33,8 +33,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>NOMBRE DEL PROCESO</t>
   </si>
@@ -133,13 +155,37 @@
   </si>
   <si>
     <t>HOJA DE OPERACIÓN ESTANDAR ( DISTRIBUCIÓN )</t>
+  </si>
+  <si>
+    <t>CANTIDAD</t>
+  </si>
+  <si>
+    <t>TIEMPO</t>
+  </si>
+  <si>
+    <t>TIEMPO ADICIONAL</t>
+  </si>
+  <si>
+    <t>TOMA DE PARTES</t>
+  </si>
+  <si>
+    <t>DEJAR PARTES</t>
+  </si>
+  <si>
+    <t>PASOS</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>SAFETY EQUIPMENT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -229,8 +275,16 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -240,8 +294,14 @@
     <fill>
       <patternFill patternType="mediumGray"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="46">
+  <borders count="50">
     <border>
       <left/>
       <right/>
@@ -556,19 +616,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -722,9 +769,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -736,17 +781,6 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -775,6 +809,80 @@
         <color indexed="64"/>
       </right>
       <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
@@ -786,7 +894,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="156">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
       <protection locked="0"/>
@@ -795,385 +903,462 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1197,15 +1382,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>590966</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>207682</xdr:rowOff>
+      <xdr:colOff>836711</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>205777</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1234,8 +1419,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8467725" y="3590925"/>
-          <a:ext cx="398561" cy="426757"/>
+          <a:off x="8229600" y="8791575"/>
+          <a:ext cx="417611" cy="434377"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1247,15 +1432,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>211105</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>211108</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>131095</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>216823</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1284,8 +1469,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9267825" y="3619500"/>
-          <a:ext cx="363505" cy="390178"/>
+          <a:off x="9286875" y="8829675"/>
+          <a:ext cx="350170" cy="407323"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1296,23 +1481,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>628692</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>173387</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>579541</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>187482</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 7">
+        <xdr:cNvPr id="10" name="Picture 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6BB853A-CB3B-2B7C-87A1-93A1FFDE136B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{208CE789-E3AC-A325-2431-C7482BDDCB2B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1334,8 +1519,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9953625" y="3609975"/>
-          <a:ext cx="483912" cy="373412"/>
+          <a:off x="10401300" y="8858250"/>
+          <a:ext cx="484291" cy="349407"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1346,23 +1531,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>293370</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>220979</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>629071</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>187482</xdr:rowOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>233302</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>149411</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 9">
+        <xdr:cNvPr id="12" name="Picture 11">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{208CE789-E3AC-A325-2431-C7482BDDCB2B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{670980EB-0BCF-7084-0468-9EF00535AE85}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1384,8 +1569,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10734675" y="3648075"/>
-          <a:ext cx="465241" cy="349407"/>
+          <a:off x="11437620" y="3469004"/>
+          <a:ext cx="475237" cy="278952"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1394,57 +1579,144 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>131445</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>211454</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>416182</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>137981</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>942975</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Picture 11">
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Plus 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{670980EB-0BCF-7084-0468-9EF00535AE85}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{616B7A48-F69C-4CE0-BC63-AFED76D16693}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11475720" y="3669029"/>
-          <a:ext cx="484762" cy="278952"/>
+          <a:off x="8086725" y="8743950"/>
+          <a:ext cx="666750" cy="657225"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom prst="mathPlus">
           <a:avLst/>
         </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="00B050"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="00B050"/>
+          </a:solidFill>
+        </a:ln>
       </xdr:spPr>
-    </xdr:pic>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1764,33 +2036,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5A05750-1890-407F-BA4E-DCBFAEC32B37}">
-  <dimension ref="B1:Z19"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B1:Z72"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" customWidth="1"/>
-    <col min="2" max="2" width="5.109375" customWidth="1"/>
-    <col min="3" max="5" width="13.44140625" customWidth="1"/>
-    <col min="6" max="6" width="5.109375" customWidth="1"/>
-    <col min="7" max="7" width="5.5546875" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" customWidth="1"/>
+    <col min="2" max="2" width="5.140625" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" customWidth="1"/>
+    <col min="5" max="5" width="0.7109375" customWidth="1"/>
+    <col min="6" max="6" width="23.5703125" customWidth="1"/>
+    <col min="7" max="7" width="5.5703125" customWidth="1"/>
     <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" customWidth="1"/>
-    <col min="10" max="10" width="6.77734375" customWidth="1"/>
-    <col min="11" max="14" width="4.88671875" customWidth="1"/>
-    <col min="15" max="15" width="1.33203125" customWidth="1"/>
-    <col min="16" max="16" width="3.6640625" customWidth="1"/>
-    <col min="17" max="17" width="4.88671875" customWidth="1"/>
-    <col min="18" max="18" width="2.5546875" customWidth="1"/>
-    <col min="19" max="19" width="11.109375" customWidth="1"/>
-    <col min="20" max="20" width="3.88671875" customWidth="1"/>
-    <col min="21" max="21" width="1.5546875" customWidth="1"/>
-    <col min="22" max="22" width="5.88671875" customWidth="1"/>
-    <col min="23" max="24" width="11.109375" customWidth="1"/>
-    <col min="25" max="25" width="2.88671875" customWidth="1"/>
-    <col min="26" max="26" width="8.33203125" customWidth="1"/>
-    <col min="27" max="27" width="1.6640625" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" customWidth="1"/>
+    <col min="11" max="14" width="4.85546875" customWidth="1"/>
+    <col min="15" max="15" width="1.28515625" customWidth="1"/>
+    <col min="16" max="16" width="3.7109375" customWidth="1"/>
+    <col min="17" max="18" width="4.85546875" customWidth="1"/>
+    <col min="19" max="19" width="18.42578125" customWidth="1"/>
+    <col min="20" max="20" width="7" customWidth="1"/>
+    <col min="21" max="21" width="6.42578125" customWidth="1"/>
+    <col min="22" max="22" width="8.5703125" customWidth="1"/>
+    <col min="23" max="23" width="6.42578125" customWidth="1"/>
+    <col min="24" max="24" width="9.42578125" customWidth="1"/>
+    <col min="25" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="8.7109375" customWidth="1"/>
+    <col min="27" max="27" width="1.7109375" customWidth="1"/>
+    <col min="29" max="29" width="4.85546875" customWidth="1"/>
+    <col min="30" max="30" width="3.85546875" customWidth="1"/>
+    <col min="31" max="31" width="2.5703125" customWidth="1"/>
+    <col min="32" max="32" width="2.7109375" customWidth="1"/>
+    <col min="33" max="33" width="4.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
@@ -1817,36 +2096,36 @@
       <c r="Y1" s="3"/>
       <c r="Z1" s="3"/>
     </row>
-    <row r="2" spans="2:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="120" t="s">
+    <row r="2" spans="2:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="126" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="120"/>
-      <c r="D2" s="120"/>
-      <c r="E2" s="120"/>
-      <c r="F2" s="120"/>
-      <c r="G2" s="120"/>
-      <c r="H2" s="120"/>
-      <c r="I2" s="120"/>
-      <c r="J2" s="120"/>
-      <c r="K2" s="120"/>
-      <c r="L2" s="120"/>
-      <c r="M2" s="120"/>
-      <c r="N2" s="120"/>
-      <c r="O2" s="120"/>
-      <c r="P2" s="120"/>
-      <c r="Q2" s="120"/>
-      <c r="R2" s="120"/>
-      <c r="S2" s="120"/>
-      <c r="T2" s="120"/>
-      <c r="U2" s="120"/>
-      <c r="V2" s="120"/>
-      <c r="W2" s="120"/>
-      <c r="X2" s="120"/>
-      <c r="Y2" s="120"/>
-      <c r="Z2" s="120"/>
-    </row>
-    <row r="3" spans="2:26" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="126"/>
+      <c r="D2" s="126"/>
+      <c r="E2" s="126"/>
+      <c r="F2" s="126"/>
+      <c r="G2" s="126"/>
+      <c r="H2" s="126"/>
+      <c r="I2" s="126"/>
+      <c r="J2" s="126"/>
+      <c r="K2" s="126"/>
+      <c r="L2" s="126"/>
+      <c r="M2" s="126"/>
+      <c r="N2" s="126"/>
+      <c r="O2" s="126"/>
+      <c r="P2" s="126"/>
+      <c r="Q2" s="126"/>
+      <c r="R2" s="126"/>
+      <c r="S2" s="126"/>
+      <c r="T2" s="126"/>
+      <c r="U2" s="126"/>
+      <c r="V2" s="126"/>
+      <c r="W2" s="126"/>
+      <c r="X2" s="126"/>
+      <c r="Y2" s="126"/>
+      <c r="Z2" s="126"/>
+    </row>
+    <row r="3" spans="2:26" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -1873,7 +2152,7 @@
       <c r="Y3" s="3"/>
       <c r="Z3" s="3"/>
     </row>
-    <row r="4" spans="2:26" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:26" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -1900,7 +2179,7 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" spans="2:26" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:26" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -1927,7 +2206,7 @@
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
     </row>
-    <row r="6" spans="2:26" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:26" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -1954,203 +2233,203 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
     </row>
-    <row r="7" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="70" t="s">
+    <row r="7" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="71"/>
-      <c r="D7" s="71"/>
-      <c r="E7" s="71"/>
-      <c r="F7" s="72"/>
-      <c r="G7" s="64" t="s">
+      <c r="C7" s="65"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="65"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="110" t="s">
         <v>1</v>
       </c>
-      <c r="H7" s="65"/>
-      <c r="I7" s="65"/>
-      <c r="J7" s="65"/>
-      <c r="K7" s="40" t="s">
+      <c r="H7" s="111"/>
+      <c r="I7" s="111"/>
+      <c r="J7" s="111"/>
+      <c r="K7" s="135" t="s">
         <v>5</v>
       </c>
-      <c r="L7" s="41"/>
-      <c r="M7" s="77" t="s">
+      <c r="L7" s="149"/>
+      <c r="M7" s="95" t="s">
         <v>22</v>
       </c>
-      <c r="N7" s="77"/>
-      <c r="O7" s="77"/>
-      <c r="P7" s="77"/>
-      <c r="Q7" s="77"/>
-      <c r="R7" s="77"/>
-      <c r="S7" s="77"/>
-      <c r="T7" s="77"/>
-      <c r="U7" s="77"/>
-      <c r="V7" s="40" t="s">
+      <c r="N7" s="95"/>
+      <c r="O7" s="95"/>
+      <c r="P7" s="95"/>
+      <c r="Q7" s="95"/>
+      <c r="R7" s="95"/>
+      <c r="S7" s="95"/>
+      <c r="T7" s="95"/>
+      <c r="U7" s="95"/>
+      <c r="V7" s="135" t="s">
         <v>23</v>
       </c>
-      <c r="W7" s="129"/>
-      <c r="X7" s="129"/>
-      <c r="Y7" s="129"/>
-      <c r="Z7" s="130"/>
-    </row>
-    <row r="8" spans="2:26" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B8" s="73"/>
-      <c r="C8" s="74"/>
-      <c r="D8" s="74"/>
-      <c r="E8" s="74"/>
-      <c r="F8" s="75"/>
-      <c r="G8" s="66"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="67"/>
-      <c r="J8" s="67"/>
-      <c r="K8" s="42"/>
-      <c r="L8" s="43"/>
-      <c r="M8" s="61"/>
-      <c r="N8" s="62"/>
-      <c r="O8" s="62"/>
-      <c r="P8" s="62"/>
-      <c r="Q8" s="62"/>
-      <c r="R8" s="62"/>
-      <c r="S8" s="62"/>
-      <c r="T8" s="62"/>
-      <c r="U8" s="63"/>
-      <c r="V8" s="115"/>
-      <c r="W8" s="115"/>
-      <c r="X8" s="115"/>
-      <c r="Y8" s="115"/>
-      <c r="Z8" s="116"/>
-    </row>
-    <row r="9" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B9" s="31" t="s">
+      <c r="W7" s="136"/>
+      <c r="X7" s="136"/>
+      <c r="Y7" s="136"/>
+      <c r="Z7" s="137"/>
+    </row>
+    <row r="8" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="67"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="112"/>
+      <c r="H8" s="113"/>
+      <c r="I8" s="113"/>
+      <c r="J8" s="113"/>
+      <c r="K8" s="150"/>
+      <c r="L8" s="151"/>
+      <c r="M8" s="89"/>
+      <c r="N8" s="90"/>
+      <c r="O8" s="90"/>
+      <c r="P8" s="90"/>
+      <c r="Q8" s="90"/>
+      <c r="R8" s="90"/>
+      <c r="S8" s="90"/>
+      <c r="T8" s="90"/>
+      <c r="U8" s="91"/>
+      <c r="V8" s="102"/>
+      <c r="W8" s="102"/>
+      <c r="X8" s="102"/>
+      <c r="Y8" s="102"/>
+      <c r="Z8" s="103"/>
+    </row>
+    <row r="9" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B9" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="32"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="34" t="s">
+      <c r="C9" s="77"/>
+      <c r="D9" s="78"/>
+      <c r="E9" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="F9" s="33"/>
-      <c r="G9" s="34" t="s">
+      <c r="F9" s="78"/>
+      <c r="G9" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="33"/>
-      <c r="K9" s="44"/>
-      <c r="L9" s="45"/>
-      <c r="M9" s="61"/>
-      <c r="N9" s="62"/>
-      <c r="O9" s="62"/>
-      <c r="P9" s="62"/>
-      <c r="Q9" s="62"/>
-      <c r="R9" s="62"/>
-      <c r="S9" s="62"/>
-      <c r="T9" s="62"/>
-      <c r="U9" s="63"/>
-      <c r="V9" s="62"/>
-      <c r="W9" s="62"/>
-      <c r="X9" s="62"/>
-      <c r="Y9" s="62"/>
-      <c r="Z9" s="117"/>
-    </row>
-    <row r="10" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B10" s="35"/>
-      <c r="C10" s="36"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="61"/>
-      <c r="H10" s="62"/>
-      <c r="I10" s="62"/>
-      <c r="J10" s="63"/>
-      <c r="K10" s="46"/>
-      <c r="L10" s="43"/>
-      <c r="M10" s="61"/>
-      <c r="N10" s="62"/>
-      <c r="O10" s="62"/>
-      <c r="P10" s="62"/>
-      <c r="Q10" s="62"/>
-      <c r="R10" s="62"/>
-      <c r="S10" s="62"/>
-      <c r="T10" s="62"/>
-      <c r="U10" s="63"/>
-      <c r="V10" s="118"/>
-      <c r="W10" s="119"/>
-      <c r="X10" s="62"/>
-      <c r="Y10" s="62"/>
-      <c r="Z10" s="117"/>
-    </row>
-    <row r="11" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B11" s="39" t="s">
+      <c r="H9" s="77"/>
+      <c r="I9" s="77"/>
+      <c r="J9" s="78"/>
+      <c r="K9" s="152"/>
+      <c r="L9" s="153"/>
+      <c r="M9" s="89"/>
+      <c r="N9" s="90"/>
+      <c r="O9" s="90"/>
+      <c r="P9" s="90"/>
+      <c r="Q9" s="90"/>
+      <c r="R9" s="90"/>
+      <c r="S9" s="90"/>
+      <c r="T9" s="90"/>
+      <c r="U9" s="91"/>
+      <c r="V9" s="90"/>
+      <c r="W9" s="90"/>
+      <c r="X9" s="90"/>
+      <c r="Y9" s="90"/>
+      <c r="Z9" s="104"/>
+    </row>
+    <row r="10" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B10" s="80"/>
+      <c r="C10" s="81"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="89"/>
+      <c r="H10" s="90"/>
+      <c r="I10" s="90"/>
+      <c r="J10" s="91"/>
+      <c r="K10" s="154"/>
+      <c r="L10" s="151"/>
+      <c r="M10" s="89"/>
+      <c r="N10" s="90"/>
+      <c r="O10" s="90"/>
+      <c r="P10" s="90"/>
+      <c r="Q10" s="90"/>
+      <c r="R10" s="90"/>
+      <c r="S10" s="90"/>
+      <c r="T10" s="90"/>
+      <c r="U10" s="91"/>
+      <c r="V10" s="105"/>
+      <c r="W10" s="106"/>
+      <c r="X10" s="90"/>
+      <c r="Y10" s="90"/>
+      <c r="Z10" s="104"/>
+    </row>
+    <row r="11" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B11" s="82" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="28"/>
-      <c r="D11" s="26" t="s">
+      <c r="C11" s="72"/>
+      <c r="D11" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="27"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="68" t="s">
+      <c r="E11" s="71"/>
+      <c r="F11" s="72"/>
+      <c r="G11" s="92" t="s">
         <v>26</v>
       </c>
-      <c r="H11" s="69"/>
-      <c r="I11" s="15" t="s">
+      <c r="H11" s="93"/>
+      <c r="I11" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="J11" s="26" t="s">
+      <c r="J11" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="K11" s="27"/>
-      <c r="L11" s="27"/>
-      <c r="M11" s="27"/>
-      <c r="N11" s="27"/>
-      <c r="O11" s="27"/>
-      <c r="P11" s="91" t="s">
+      <c r="K11" s="71"/>
+      <c r="L11" s="71"/>
+      <c r="M11" s="71"/>
+      <c r="N11" s="71"/>
+      <c r="O11" s="71"/>
+      <c r="P11" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="Q11" s="92"/>
-      <c r="R11" s="92"/>
-      <c r="S11" s="92"/>
-      <c r="T11" s="92"/>
-      <c r="U11" s="91" t="s">
+      <c r="Q11" s="108"/>
+      <c r="R11" s="108"/>
+      <c r="S11" s="108"/>
+      <c r="T11" s="108"/>
+      <c r="U11" s="107" t="s">
         <v>30</v>
       </c>
-      <c r="V11" s="92"/>
-      <c r="W11" s="93"/>
-      <c r="X11" s="94" t="s">
+      <c r="V11" s="108"/>
+      <c r="W11" s="109"/>
+      <c r="X11" s="146" t="s">
         <v>31</v>
       </c>
-      <c r="Y11" s="95"/>
-      <c r="Z11" s="96"/>
-    </row>
-    <row r="12" spans="2:26" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="24"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="25"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="88"/>
-      <c r="K12" s="89"/>
-      <c r="L12" s="89"/>
-      <c r="M12" s="89"/>
-      <c r="N12" s="89"/>
-      <c r="O12" s="89"/>
-      <c r="P12" s="88"/>
-      <c r="Q12" s="89"/>
-      <c r="R12" s="89"/>
-      <c r="S12" s="89"/>
-      <c r="T12" s="90"/>
-      <c r="U12" s="88"/>
-      <c r="V12" s="89"/>
-      <c r="W12" s="90"/>
-      <c r="X12" s="20"/>
-      <c r="Y12" s="6" t="s">
+      <c r="Y11" s="147"/>
+      <c r="Z11" s="148"/>
+    </row>
+    <row r="12" spans="2:26" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="83"/>
+      <c r="C12" s="75"/>
+      <c r="D12" s="73"/>
+      <c r="E12" s="74"/>
+      <c r="F12" s="75"/>
+      <c r="G12" s="73"/>
+      <c r="H12" s="75"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="100"/>
+      <c r="K12" s="101"/>
+      <c r="L12" s="101"/>
+      <c r="M12" s="101"/>
+      <c r="N12" s="101"/>
+      <c r="O12" s="101"/>
+      <c r="P12" s="100"/>
+      <c r="Q12" s="101"/>
+      <c r="R12" s="101"/>
+      <c r="S12" s="101"/>
+      <c r="T12" s="117"/>
+      <c r="U12" s="100"/>
+      <c r="V12" s="101"/>
+      <c r="W12" s="117"/>
+      <c r="X12" s="12"/>
+      <c r="Y12" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z12" s="21"/>
-    </row>
-    <row r="13" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Z12" s="13"/>
+    </row>
+    <row r="13" spans="2:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
@@ -2177,247 +2456,1253 @@
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
     </row>
-    <row r="14" spans="2:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="59" t="s">
+    <row r="14" spans="2:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="76" t="s">
+      <c r="C14" s="94" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="77"/>
-      <c r="E14" s="77"/>
-      <c r="F14" s="77"/>
-      <c r="G14" s="78"/>
-      <c r="H14" s="76" t="s">
+      <c r="D14" s="95"/>
+      <c r="E14" s="95"/>
+      <c r="F14" s="95"/>
+      <c r="G14" s="94" t="s">
         <v>17</v>
       </c>
-      <c r="I14" s="77"/>
-      <c r="J14" s="77"/>
-      <c r="K14" s="78"/>
-      <c r="L14" s="109" t="s">
+      <c r="H14" s="95"/>
+      <c r="I14" s="95"/>
+      <c r="J14" s="95"/>
+      <c r="K14" s="96"/>
+      <c r="L14" s="122" t="s">
         <v>16</v>
       </c>
-      <c r="M14" s="110"/>
-      <c r="N14" s="110"/>
-      <c r="O14" s="110"/>
-      <c r="P14" s="110"/>
-      <c r="Q14" s="110"/>
-      <c r="R14" s="76" t="s">
+      <c r="M14" s="123"/>
+      <c r="N14" s="123"/>
+      <c r="O14" s="123"/>
+      <c r="P14" s="123"/>
+      <c r="Q14" s="123"/>
+      <c r="R14" s="94" t="s">
         <v>15</v>
       </c>
-      <c r="S14" s="77"/>
-      <c r="T14" s="77"/>
-      <c r="U14" s="77"/>
-      <c r="V14" s="77"/>
-      <c r="W14" s="77"/>
-      <c r="X14" s="77"/>
-      <c r="Y14" s="77"/>
-      <c r="Z14" s="105"/>
-    </row>
-    <row r="15" spans="2:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="60"/>
-      <c r="C15" s="79" t="s">
+      <c r="S14" s="95"/>
+      <c r="T14" s="95"/>
+      <c r="U14" s="95"/>
+      <c r="V14" s="95"/>
+      <c r="W14" s="95"/>
+      <c r="X14" s="95"/>
+      <c r="Y14" s="95"/>
+      <c r="Z14" s="124"/>
+    </row>
+    <row r="15" spans="2:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="88"/>
+      <c r="C15" s="97" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="80"/>
-      <c r="E15" s="80"/>
-      <c r="F15" s="80"/>
-      <c r="G15" s="81"/>
-      <c r="H15" s="79"/>
-      <c r="I15" s="80"/>
-      <c r="J15" s="80"/>
-      <c r="K15" s="81"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="16"/>
-      <c r="O15" s="36"/>
-      <c r="P15" s="37"/>
-      <c r="Q15" s="4"/>
-      <c r="R15" s="79"/>
-      <c r="S15" s="80"/>
-      <c r="T15" s="80"/>
-      <c r="U15" s="80"/>
-      <c r="V15" s="80"/>
-      <c r="W15" s="80"/>
-      <c r="X15" s="80"/>
-      <c r="Y15" s="80"/>
-      <c r="Z15" s="106"/>
-    </row>
-    <row r="16" spans="2:26" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="22"/>
-      <c r="C16" s="82"/>
-      <c r="D16" s="83"/>
-      <c r="E16" s="83"/>
-      <c r="F16" s="83"/>
-      <c r="G16" s="84"/>
-      <c r="H16" s="82"/>
-      <c r="I16" s="83"/>
-      <c r="J16" s="83"/>
-      <c r="K16" s="84"/>
-      <c r="L16" s="17"/>
-      <c r="M16" s="17"/>
-      <c r="N16" s="17"/>
-      <c r="O16" s="107"/>
-      <c r="P16" s="108"/>
-      <c r="Q16" s="17"/>
-      <c r="Z16" s="14"/>
-    </row>
-    <row r="17" spans="2:26" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="23"/>
-      <c r="C17" s="85"/>
-      <c r="D17" s="86"/>
-      <c r="E17" s="86"/>
-      <c r="F17" s="86"/>
-      <c r="G17" s="87"/>
-      <c r="H17" s="85"/>
-      <c r="I17" s="86"/>
-      <c r="J17" s="86"/>
-      <c r="K17" s="87"/>
-      <c r="L17" s="18"/>
-      <c r="M17" s="19"/>
-      <c r="N17" s="19"/>
-      <c r="O17" s="103"/>
-      <c r="P17" s="104"/>
-      <c r="Q17" s="5"/>
-      <c r="R17" s="99" t="s">
+      <c r="D15" s="98"/>
+      <c r="E15" s="98"/>
+      <c r="F15" s="98"/>
+      <c r="G15" s="97"/>
+      <c r="H15" s="98"/>
+      <c r="I15" s="98"/>
+      <c r="J15" s="98"/>
+      <c r="K15" s="99"/>
+      <c r="L15" s="21"/>
+      <c r="M15" s="21"/>
+      <c r="N15" s="21"/>
+      <c r="O15" s="120"/>
+      <c r="P15" s="121"/>
+      <c r="Q15" s="22"/>
+      <c r="R15" s="97"/>
+      <c r="S15" s="98"/>
+      <c r="T15" s="98"/>
+      <c r="U15" s="98"/>
+      <c r="V15" s="98"/>
+      <c r="W15" s="98"/>
+      <c r="X15" s="98"/>
+      <c r="Y15" s="98"/>
+      <c r="Z15" s="125"/>
+    </row>
+    <row r="16" spans="2:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="32"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="42"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="43"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="39"/>
+      <c r="P16" s="40"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="141"/>
+      <c r="S16" s="142"/>
+      <c r="T16" s="142"/>
+      <c r="U16" s="142"/>
+      <c r="V16" s="142"/>
+      <c r="W16" s="142"/>
+      <c r="X16" s="142"/>
+      <c r="Y16" s="142"/>
+      <c r="Z16" s="143"/>
+    </row>
+    <row r="17" spans="2:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="32"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="42"/>
+      <c r="K17" s="43"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="27"/>
+      <c r="N17" s="27"/>
+      <c r="O17" s="39"/>
+      <c r="P17" s="40"/>
+      <c r="Q17" s="10"/>
+      <c r="R17" s="56"/>
+      <c r="S17" s="155"/>
+      <c r="T17" s="155"/>
+      <c r="U17" s="155"/>
+      <c r="V17" s="155"/>
+      <c r="W17" s="155"/>
+      <c r="X17" s="155"/>
+      <c r="Y17" s="155"/>
+      <c r="Z17" s="58"/>
+    </row>
+    <row r="18" spans="2:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="32"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="42"/>
+      <c r="K18" s="43"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="27"/>
+      <c r="N18" s="27"/>
+      <c r="O18" s="39"/>
+      <c r="P18" s="40"/>
+      <c r="Q18" s="10"/>
+      <c r="R18" s="56"/>
+      <c r="S18" s="155"/>
+      <c r="T18" s="155"/>
+      <c r="U18" s="155"/>
+      <c r="V18" s="155"/>
+      <c r="W18" s="155"/>
+      <c r="X18" s="155"/>
+      <c r="Y18" s="155"/>
+      <c r="Z18" s="58"/>
+    </row>
+    <row r="19" spans="2:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="32"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="42"/>
+      <c r="J19" s="42"/>
+      <c r="K19" s="43"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="27"/>
+      <c r="N19" s="27"/>
+      <c r="O19" s="39"/>
+      <c r="P19" s="40"/>
+      <c r="Q19" s="10"/>
+      <c r="R19" s="56"/>
+      <c r="S19" s="155"/>
+      <c r="T19" s="155"/>
+      <c r="U19" s="155"/>
+      <c r="V19" s="155"/>
+      <c r="W19" s="155"/>
+      <c r="X19" s="155"/>
+      <c r="Y19" s="155"/>
+      <c r="Z19" s="58"/>
+    </row>
+    <row r="20" spans="2:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="32"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="42"/>
+      <c r="K20" s="43"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="27"/>
+      <c r="N20" s="27"/>
+      <c r="O20" s="39"/>
+      <c r="P20" s="40"/>
+      <c r="Q20" s="10"/>
+      <c r="R20" s="56"/>
+      <c r="S20" s="155"/>
+      <c r="T20" s="155"/>
+      <c r="U20" s="155"/>
+      <c r="V20" s="155"/>
+      <c r="W20" s="155"/>
+      <c r="X20" s="155"/>
+      <c r="Y20" s="155"/>
+      <c r="Z20" s="58"/>
+    </row>
+    <row r="21" spans="2:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="32"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="42"/>
+      <c r="K21" s="43"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="27"/>
+      <c r="N21" s="27"/>
+      <c r="O21" s="39"/>
+      <c r="P21" s="40"/>
+      <c r="Q21" s="10"/>
+      <c r="R21" s="56"/>
+      <c r="S21" s="155"/>
+      <c r="T21" s="155"/>
+      <c r="U21" s="155"/>
+      <c r="V21" s="155"/>
+      <c r="W21" s="155"/>
+      <c r="X21" s="155"/>
+      <c r="Y21" s="155"/>
+      <c r="Z21" s="58"/>
+    </row>
+    <row r="22" spans="2:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="32"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="42"/>
+      <c r="K22" s="43"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="27"/>
+      <c r="N22" s="27"/>
+      <c r="O22" s="39"/>
+      <c r="P22" s="40"/>
+      <c r="Q22" s="10"/>
+      <c r="R22" s="56"/>
+      <c r="S22" s="155"/>
+      <c r="T22" s="155"/>
+      <c r="U22" s="155"/>
+      <c r="V22" s="155"/>
+      <c r="W22" s="155"/>
+      <c r="X22" s="155"/>
+      <c r="Y22" s="155"/>
+      <c r="Z22" s="58"/>
+    </row>
+    <row r="23" spans="2:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="32"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="42"/>
+      <c r="K23" s="43"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="27"/>
+      <c r="N23" s="27"/>
+      <c r="O23" s="39"/>
+      <c r="P23" s="40"/>
+      <c r="Q23" s="10"/>
+      <c r="R23" s="56"/>
+      <c r="S23" s="155"/>
+      <c r="T23" s="155"/>
+      <c r="U23" s="155"/>
+      <c r="V23" s="155"/>
+      <c r="W23" s="155"/>
+      <c r="X23" s="155"/>
+      <c r="Y23" s="155"/>
+      <c r="Z23" s="58"/>
+    </row>
+    <row r="24" spans="2:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="32"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="42"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="42"/>
+      <c r="I24" s="42"/>
+      <c r="J24" s="42"/>
+      <c r="K24" s="43"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="27"/>
+      <c r="N24" s="27"/>
+      <c r="O24" s="39"/>
+      <c r="P24" s="40"/>
+      <c r="Q24" s="10"/>
+      <c r="R24" s="56"/>
+      <c r="S24" s="155"/>
+      <c r="T24" s="155"/>
+      <c r="U24" s="155"/>
+      <c r="V24" s="155"/>
+      <c r="W24" s="155"/>
+      <c r="X24" s="155"/>
+      <c r="Y24" s="155"/>
+      <c r="Z24" s="58"/>
+    </row>
+    <row r="25" spans="2:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="32"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="42"/>
+      <c r="K25" s="43"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="27"/>
+      <c r="N25" s="27"/>
+      <c r="O25" s="39"/>
+      <c r="P25" s="40"/>
+      <c r="Q25" s="10"/>
+      <c r="R25" s="56"/>
+      <c r="S25" s="155"/>
+      <c r="T25" s="57"/>
+      <c r="U25" s="57"/>
+      <c r="V25" s="57"/>
+      <c r="W25" s="57"/>
+      <c r="X25" s="57"/>
+      <c r="Y25" s="57"/>
+      <c r="Z25" s="58"/>
+    </row>
+    <row r="26" spans="2:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="32"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="42"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="42"/>
+      <c r="I26" s="42"/>
+      <c r="J26" s="42"/>
+      <c r="K26" s="43"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="27"/>
+      <c r="N26" s="27"/>
+      <c r="O26" s="39"/>
+      <c r="P26" s="40"/>
+      <c r="Q26" s="10"/>
+      <c r="R26" s="56"/>
+      <c r="S26" s="155"/>
+      <c r="T26" s="57"/>
+      <c r="U26" s="57"/>
+      <c r="V26" s="57"/>
+      <c r="W26" s="57"/>
+      <c r="X26" s="57"/>
+      <c r="Y26" s="57"/>
+      <c r="Z26" s="58"/>
+    </row>
+    <row r="27" spans="2:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="32"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="42"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="42"/>
+      <c r="I27" s="42"/>
+      <c r="J27" s="42"/>
+      <c r="K27" s="43"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="27"/>
+      <c r="N27" s="27"/>
+      <c r="O27" s="39"/>
+      <c r="P27" s="40"/>
+      <c r="Q27" s="10"/>
+      <c r="R27" s="56"/>
+      <c r="S27" s="155"/>
+      <c r="T27" s="57"/>
+      <c r="U27" s="57"/>
+      <c r="V27" s="57"/>
+      <c r="W27" s="57"/>
+      <c r="X27" s="57"/>
+      <c r="Y27" s="57"/>
+      <c r="Z27" s="58"/>
+    </row>
+    <row r="28" spans="2:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="32"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="42"/>
+      <c r="E28" s="42"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="42"/>
+      <c r="I28" s="42"/>
+      <c r="J28" s="42"/>
+      <c r="K28" s="43"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="27"/>
+      <c r="N28" s="27"/>
+      <c r="O28" s="39"/>
+      <c r="P28" s="40"/>
+      <c r="Q28" s="10"/>
+      <c r="R28" s="56"/>
+      <c r="S28" s="155"/>
+      <c r="T28" s="57"/>
+      <c r="U28" s="57"/>
+      <c r="V28" s="57"/>
+      <c r="W28" s="57"/>
+      <c r="X28" s="57"/>
+      <c r="Y28" s="57"/>
+      <c r="Z28" s="58"/>
+    </row>
+    <row r="29" spans="2:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="32"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="42"/>
+      <c r="F29" s="42"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="42"/>
+      <c r="I29" s="42"/>
+      <c r="J29" s="42"/>
+      <c r="K29" s="43"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="27"/>
+      <c r="N29" s="27"/>
+      <c r="O29" s="39"/>
+      <c r="P29" s="40"/>
+      <c r="Q29" s="10"/>
+      <c r="R29" s="56"/>
+      <c r="S29" s="155"/>
+      <c r="T29" s="57"/>
+      <c r="U29" s="57"/>
+      <c r="V29" s="57"/>
+      <c r="W29" s="57"/>
+      <c r="X29" s="57"/>
+      <c r="Y29" s="57"/>
+      <c r="Z29" s="58"/>
+    </row>
+    <row r="30" spans="2:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="32"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="42"/>
+      <c r="F30" s="42"/>
+      <c r="G30" s="41"/>
+      <c r="H30" s="42"/>
+      <c r="I30" s="42"/>
+      <c r="J30" s="42"/>
+      <c r="K30" s="43"/>
+      <c r="L30" s="10"/>
+      <c r="M30" s="27"/>
+      <c r="N30" s="27"/>
+      <c r="O30" s="39"/>
+      <c r="P30" s="40"/>
+      <c r="Q30" s="10"/>
+      <c r="R30" s="56"/>
+      <c r="S30" s="155"/>
+      <c r="T30" s="57"/>
+      <c r="U30" s="57"/>
+      <c r="V30" s="57"/>
+      <c r="W30" s="57"/>
+      <c r="X30" s="57"/>
+      <c r="Y30" s="57"/>
+      <c r="Z30" s="58"/>
+    </row>
+    <row r="31" spans="2:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="32"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="42"/>
+      <c r="E31" s="42"/>
+      <c r="F31" s="42"/>
+      <c r="G31" s="41"/>
+      <c r="H31" s="42"/>
+      <c r="I31" s="42"/>
+      <c r="J31" s="42"/>
+      <c r="K31" s="43"/>
+      <c r="L31" s="10"/>
+      <c r="M31" s="27"/>
+      <c r="N31" s="27"/>
+      <c r="O31" s="39"/>
+      <c r="P31" s="40"/>
+      <c r="Q31" s="10"/>
+      <c r="R31" s="56"/>
+      <c r="S31" s="155"/>
+      <c r="T31" s="57"/>
+      <c r="U31" s="57"/>
+      <c r="V31" s="57"/>
+      <c r="W31" s="57"/>
+      <c r="X31" s="57"/>
+      <c r="Y31" s="57"/>
+      <c r="Z31" s="58"/>
+    </row>
+    <row r="32" spans="2:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="32"/>
+      <c r="C32" s="41"/>
+      <c r="D32" s="42"/>
+      <c r="E32" s="42"/>
+      <c r="F32" s="42"/>
+      <c r="G32" s="41"/>
+      <c r="H32" s="42"/>
+      <c r="I32" s="42"/>
+      <c r="J32" s="42"/>
+      <c r="K32" s="43"/>
+      <c r="L32" s="10"/>
+      <c r="M32" s="27"/>
+      <c r="N32" s="27"/>
+      <c r="O32" s="39"/>
+      <c r="P32" s="40"/>
+      <c r="Q32" s="10"/>
+      <c r="R32" s="56"/>
+      <c r="S32" s="155"/>
+      <c r="T32" s="57"/>
+      <c r="U32" s="57"/>
+      <c r="V32" s="57"/>
+      <c r="W32" s="57"/>
+      <c r="X32" s="57"/>
+      <c r="Y32" s="57"/>
+      <c r="Z32" s="58"/>
+    </row>
+    <row r="33" spans="2:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="32"/>
+      <c r="C33" s="41"/>
+      <c r="D33" s="42"/>
+      <c r="E33" s="42"/>
+      <c r="F33" s="42"/>
+      <c r="G33" s="41"/>
+      <c r="H33" s="42"/>
+      <c r="I33" s="42"/>
+      <c r="J33" s="42"/>
+      <c r="K33" s="43"/>
+      <c r="L33" s="10"/>
+      <c r="M33" s="27"/>
+      <c r="N33" s="27"/>
+      <c r="O33" s="39"/>
+      <c r="P33" s="40"/>
+      <c r="Q33" s="10"/>
+      <c r="R33" s="56"/>
+      <c r="S33" s="155"/>
+      <c r="T33" s="57"/>
+      <c r="U33" s="57"/>
+      <c r="V33" s="57"/>
+      <c r="W33" s="57"/>
+      <c r="X33" s="57"/>
+      <c r="Y33" s="57"/>
+      <c r="Z33" s="58"/>
+    </row>
+    <row r="34" spans="2:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="32"/>
+      <c r="C34" s="41"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="41"/>
+      <c r="H34" s="42"/>
+      <c r="I34" s="42"/>
+      <c r="J34" s="42"/>
+      <c r="K34" s="43"/>
+      <c r="L34" s="10"/>
+      <c r="M34" s="27"/>
+      <c r="N34" s="27"/>
+      <c r="O34" s="39"/>
+      <c r="P34" s="40"/>
+      <c r="Q34" s="10"/>
+      <c r="R34" s="28"/>
+      <c r="S34" s="28"/>
+      <c r="T34" s="28"/>
+      <c r="U34" s="28"/>
+      <c r="V34" s="28"/>
+      <c r="W34" s="28"/>
+      <c r="X34" s="28"/>
+      <c r="Y34" s="28"/>
+      <c r="Z34" s="29"/>
+    </row>
+    <row r="35" spans="2:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="32"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="42"/>
+      <c r="E35" s="42"/>
+      <c r="F35" s="42"/>
+      <c r="G35" s="41"/>
+      <c r="H35" s="42"/>
+      <c r="I35" s="42"/>
+      <c r="J35" s="42"/>
+      <c r="K35" s="43"/>
+      <c r="L35" s="10"/>
+      <c r="M35" s="27"/>
+      <c r="N35" s="27"/>
+      <c r="O35" s="39"/>
+      <c r="P35" s="40"/>
+      <c r="Q35" s="10"/>
+      <c r="R35" s="28"/>
+      <c r="S35" s="20"/>
+      <c r="T35" s="59" t="s">
+        <v>33</v>
+      </c>
+      <c r="U35" s="59"/>
+      <c r="V35" s="59"/>
+      <c r="W35" s="59"/>
+      <c r="X35" s="59"/>
+      <c r="Y35" s="19"/>
+      <c r="Z35" s="29"/>
+    </row>
+    <row r="36" spans="2:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="32"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="42"/>
+      <c r="E36" s="42"/>
+      <c r="F36" s="42"/>
+      <c r="G36" s="41"/>
+      <c r="H36" s="42"/>
+      <c r="I36" s="42"/>
+      <c r="J36" s="42"/>
+      <c r="K36" s="43"/>
+      <c r="L36" s="10"/>
+      <c r="M36" s="27"/>
+      <c r="N36" s="27"/>
+      <c r="O36" s="39"/>
+      <c r="P36" s="40"/>
+      <c r="Q36" s="10"/>
+      <c r="R36" s="28"/>
+      <c r="S36" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="T36" s="25"/>
+      <c r="U36" s="25"/>
+      <c r="V36" s="16"/>
+      <c r="W36" s="16"/>
+      <c r="X36" s="16"/>
+      <c r="Y36" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z36" s="29"/>
+    </row>
+    <row r="37" spans="2:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="32"/>
+      <c r="C37" s="41"/>
+      <c r="D37" s="42"/>
+      <c r="E37" s="42"/>
+      <c r="F37" s="42"/>
+      <c r="G37" s="41"/>
+      <c r="H37" s="42"/>
+      <c r="I37" s="42"/>
+      <c r="J37" s="42"/>
+      <c r="K37" s="43"/>
+      <c r="L37" s="10"/>
+      <c r="M37" s="27"/>
+      <c r="N37" s="27"/>
+      <c r="O37" s="39"/>
+      <c r="P37" s="40"/>
+      <c r="Q37" s="10"/>
+      <c r="R37" s="28"/>
+      <c r="S37" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="T37" s="26"/>
+      <c r="U37" s="26"/>
+      <c r="V37" s="18"/>
+      <c r="W37" s="18"/>
+      <c r="X37" s="18"/>
+      <c r="Y37" s="18"/>
+      <c r="Z37" s="29"/>
+    </row>
+    <row r="38" spans="2:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="32"/>
+      <c r="C38" s="41"/>
+      <c r="D38" s="42"/>
+      <c r="E38" s="42"/>
+      <c r="F38" s="42"/>
+      <c r="G38" s="41"/>
+      <c r="H38" s="42"/>
+      <c r="I38" s="42"/>
+      <c r="J38" s="42"/>
+      <c r="K38" s="43"/>
+      <c r="L38" s="10"/>
+      <c r="M38" s="27"/>
+      <c r="N38" s="27"/>
+      <c r="O38" s="39"/>
+      <c r="P38" s="40"/>
+      <c r="Q38" s="10"/>
+      <c r="R38" s="28"/>
+      <c r="S38" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="T38" s="26"/>
+      <c r="U38" s="26"/>
+      <c r="V38" s="18"/>
+      <c r="W38" s="18"/>
+      <c r="X38" s="18"/>
+      <c r="Y38" s="18"/>
+      <c r="Z38" s="29"/>
+    </row>
+    <row r="39" spans="2:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="32"/>
+      <c r="C39" s="41"/>
+      <c r="D39" s="42"/>
+      <c r="E39" s="42"/>
+      <c r="F39" s="42"/>
+      <c r="G39" s="41"/>
+      <c r="H39" s="42"/>
+      <c r="I39" s="42"/>
+      <c r="J39" s="42"/>
+      <c r="K39" s="43"/>
+      <c r="L39" s="10"/>
+      <c r="M39" s="27"/>
+      <c r="N39" s="27"/>
+      <c r="O39" s="39"/>
+      <c r="P39" s="40"/>
+      <c r="Q39" s="10"/>
+      <c r="R39" s="28"/>
+      <c r="S39" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="T39" s="26"/>
+      <c r="U39" s="26"/>
+      <c r="V39" s="18"/>
+      <c r="W39" s="18"/>
+      <c r="X39" s="18"/>
+      <c r="Y39" s="18"/>
+      <c r="Z39" s="29"/>
+    </row>
+    <row r="40" spans="2:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="32"/>
+      <c r="C40" s="41"/>
+      <c r="D40" s="42"/>
+      <c r="E40" s="42"/>
+      <c r="F40" s="42"/>
+      <c r="G40" s="41"/>
+      <c r="H40" s="42"/>
+      <c r="I40" s="42"/>
+      <c r="J40" s="42"/>
+      <c r="K40" s="43"/>
+      <c r="L40" s="10"/>
+      <c r="M40" s="27"/>
+      <c r="N40" s="27"/>
+      <c r="O40" s="39"/>
+      <c r="P40" s="40"/>
+      <c r="Q40" s="10"/>
+      <c r="R40" s="28"/>
+      <c r="S40" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="T40" s="24"/>
+      <c r="U40" s="26"/>
+      <c r="V40" s="18"/>
+      <c r="W40" s="18"/>
+      <c r="X40" s="14"/>
+      <c r="Y40" s="15"/>
+      <c r="Z40" s="29"/>
+    </row>
+    <row r="41" spans="2:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="32"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="42"/>
+      <c r="E41" s="42"/>
+      <c r="F41" s="42"/>
+      <c r="G41" s="41"/>
+      <c r="H41" s="42"/>
+      <c r="I41" s="42"/>
+      <c r="J41" s="42"/>
+      <c r="K41" s="43"/>
+      <c r="L41" s="10"/>
+      <c r="M41" s="27"/>
+      <c r="N41" s="27"/>
+      <c r="O41" s="39"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="10"/>
+      <c r="R41" s="28"/>
+      <c r="S41" s="28"/>
+      <c r="T41" s="28"/>
+      <c r="U41" s="28"/>
+      <c r="V41" s="28"/>
+      <c r="W41" s="28"/>
+      <c r="X41" s="28"/>
+      <c r="Y41" s="28"/>
+      <c r="Z41" s="29"/>
+    </row>
+    <row r="42" spans="2:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="32"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42"/>
+      <c r="G42" s="41"/>
+      <c r="H42" s="42"/>
+      <c r="I42" s="42"/>
+      <c r="J42" s="42"/>
+      <c r="K42" s="43"/>
+      <c r="L42" s="10"/>
+      <c r="M42" s="27"/>
+      <c r="N42" s="27"/>
+      <c r="O42" s="39"/>
+      <c r="P42" s="40"/>
+      <c r="Q42" s="10"/>
+      <c r="R42" s="28"/>
+      <c r="S42" s="28"/>
+      <c r="T42" s="28"/>
+      <c r="U42" s="60" t="s">
+        <v>40</v>
+      </c>
+      <c r="V42" s="60"/>
+      <c r="W42" s="60"/>
+      <c r="X42" s="60"/>
+      <c r="Y42" s="28"/>
+      <c r="Z42" s="29"/>
+    </row>
+    <row r="43" spans="2:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="32"/>
+      <c r="C43" s="41"/>
+      <c r="D43" s="42"/>
+      <c r="E43" s="42"/>
+      <c r="F43" s="42"/>
+      <c r="G43" s="41"/>
+      <c r="H43" s="42"/>
+      <c r="I43" s="42"/>
+      <c r="J43" s="42"/>
+      <c r="K43" s="43"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="27"/>
+      <c r="N43" s="27"/>
+      <c r="O43" s="39"/>
+      <c r="P43" s="40"/>
+      <c r="Q43" s="10"/>
+      <c r="R43" s="28"/>
+      <c r="S43" s="28"/>
+      <c r="T43" s="28"/>
+      <c r="U43" s="60"/>
+      <c r="V43" s="60"/>
+      <c r="W43" s="60"/>
+      <c r="X43" s="60"/>
+      <c r="Y43" s="28"/>
+      <c r="Z43" s="29"/>
+    </row>
+    <row r="44" spans="2:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="32"/>
+      <c r="C44" s="41"/>
+      <c r="D44" s="42"/>
+      <c r="E44" s="42"/>
+      <c r="F44" s="42"/>
+      <c r="G44" s="41"/>
+      <c r="H44" s="42"/>
+      <c r="I44" s="42"/>
+      <c r="J44" s="42"/>
+      <c r="K44" s="43"/>
+      <c r="L44" s="10"/>
+      <c r="M44" s="27"/>
+      <c r="N44" s="27"/>
+      <c r="O44" s="39"/>
+      <c r="P44" s="40"/>
+      <c r="Q44" s="10"/>
+      <c r="R44" s="28"/>
+      <c r="S44" s="57"/>
+      <c r="T44" s="28"/>
+      <c r="U44" s="60"/>
+      <c r="V44" s="60"/>
+      <c r="W44" s="60"/>
+      <c r="X44" s="60"/>
+      <c r="Y44" s="28"/>
+      <c r="Z44" s="29"/>
+    </row>
+    <row r="45" spans="2:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="32"/>
+      <c r="C45" s="41"/>
+      <c r="D45" s="42"/>
+      <c r="E45" s="42"/>
+      <c r="F45" s="42"/>
+      <c r="G45" s="41"/>
+      <c r="H45" s="42"/>
+      <c r="I45" s="42"/>
+      <c r="J45" s="42"/>
+      <c r="K45" s="43"/>
+      <c r="L45" s="10"/>
+      <c r="M45" s="27"/>
+      <c r="N45" s="27"/>
+      <c r="O45" s="39"/>
+      <c r="P45" s="40"/>
+      <c r="Q45" s="10"/>
+      <c r="R45" s="28"/>
+      <c r="S45" s="57"/>
+      <c r="T45" s="28"/>
+      <c r="U45" s="60"/>
+      <c r="V45" s="60"/>
+      <c r="W45" s="60"/>
+      <c r="X45" s="60"/>
+      <c r="Y45" s="28"/>
+      <c r="Z45" s="29"/>
+    </row>
+    <row r="46" spans="2:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="32"/>
+      <c r="C46" s="41"/>
+      <c r="D46" s="42"/>
+      <c r="E46" s="42"/>
+      <c r="F46" s="42"/>
+      <c r="G46" s="41"/>
+      <c r="H46" s="42"/>
+      <c r="I46" s="42"/>
+      <c r="J46" s="42"/>
+      <c r="K46" s="43"/>
+      <c r="L46" s="10"/>
+      <c r="M46" s="27"/>
+      <c r="N46" s="27"/>
+      <c r="O46" s="39"/>
+      <c r="P46" s="40"/>
+      <c r="Q46" s="10"/>
+      <c r="R46" s="28"/>
+      <c r="S46" s="57"/>
+      <c r="T46" s="28"/>
+      <c r="U46" s="60"/>
+      <c r="V46" s="60"/>
+      <c r="W46" s="60"/>
+      <c r="X46" s="60"/>
+      <c r="Y46" s="28"/>
+      <c r="Z46" s="29"/>
+    </row>
+    <row r="47" spans="2:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="32"/>
+      <c r="C47" s="41"/>
+      <c r="D47" s="42"/>
+      <c r="E47" s="42"/>
+      <c r="F47" s="42"/>
+      <c r="G47" s="41"/>
+      <c r="H47" s="42"/>
+      <c r="I47" s="42"/>
+      <c r="J47" s="42"/>
+      <c r="K47" s="43"/>
+      <c r="L47" s="10"/>
+      <c r="M47" s="27"/>
+      <c r="N47" s="27"/>
+      <c r="O47" s="39"/>
+      <c r="P47" s="40"/>
+      <c r="Q47" s="10"/>
+      <c r="R47" s="28"/>
+      <c r="S47" s="57"/>
+      <c r="T47" s="28"/>
+      <c r="U47" s="60"/>
+      <c r="V47" s="60"/>
+      <c r="W47" s="60"/>
+      <c r="X47" s="60"/>
+      <c r="Y47" s="28"/>
+      <c r="Z47" s="29"/>
+    </row>
+    <row r="48" spans="2:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="32"/>
+      <c r="C48" s="41"/>
+      <c r="D48" s="42"/>
+      <c r="E48" s="42"/>
+      <c r="F48" s="42"/>
+      <c r="G48" s="41"/>
+      <c r="H48" s="42"/>
+      <c r="I48" s="42"/>
+      <c r="J48" s="42"/>
+      <c r="K48" s="43"/>
+      <c r="L48" s="10"/>
+      <c r="M48" s="27"/>
+      <c r="N48" s="27"/>
+      <c r="O48" s="39"/>
+      <c r="P48" s="40"/>
+      <c r="Q48" s="10"/>
+      <c r="R48" s="28"/>
+      <c r="S48" s="28"/>
+      <c r="T48" s="28"/>
+      <c r="U48" s="60"/>
+      <c r="V48" s="60"/>
+      <c r="W48" s="60"/>
+      <c r="X48" s="60"/>
+      <c r="Y48" s="28"/>
+      <c r="Z48" s="29"/>
+    </row>
+    <row r="49" spans="2:26" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="32"/>
+      <c r="C49" s="41"/>
+      <c r="D49" s="42"/>
+      <c r="E49" s="42"/>
+      <c r="F49" s="42"/>
+      <c r="G49" s="41"/>
+      <c r="H49" s="42"/>
+      <c r="I49" s="42"/>
+      <c r="J49" s="42"/>
+      <c r="K49" s="43"/>
+      <c r="L49" s="10"/>
+      <c r="M49" s="27"/>
+      <c r="N49" s="27"/>
+      <c r="O49" s="39"/>
+      <c r="P49" s="40"/>
+      <c r="Q49" s="10"/>
+      <c r="R49" s="28"/>
+      <c r="S49" s="28"/>
+      <c r="T49" s="28"/>
+      <c r="U49" s="28"/>
+      <c r="V49" s="28"/>
+      <c r="W49" s="28"/>
+      <c r="X49" s="28"/>
+      <c r="Y49" s="28"/>
+      <c r="Z49" s="29"/>
+    </row>
+    <row r="50" spans="2:26" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B50" s="33"/>
+      <c r="C50" s="138"/>
+      <c r="D50" s="139"/>
+      <c r="E50" s="139"/>
+      <c r="F50" s="139"/>
+      <c r="G50" s="138"/>
+      <c r="H50" s="139"/>
+      <c r="I50" s="139"/>
+      <c r="J50" s="139"/>
+      <c r="K50" s="140"/>
+      <c r="L50" s="30"/>
+      <c r="M50" s="11"/>
+      <c r="N50" s="11"/>
+      <c r="O50" s="118"/>
+      <c r="P50" s="119"/>
+      <c r="Q50" s="31"/>
+      <c r="R50" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="S17" s="13" t="s">
+      <c r="S50" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="T17" s="97" t="s">
+      <c r="T50" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="U17" s="102"/>
-      <c r="V17" s="98"/>
-      <c r="W17" s="13" t="s">
+      <c r="U50" s="114"/>
+      <c r="V50" s="46"/>
+      <c r="W50" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="X17" s="12" t="s">
+      <c r="X50" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="Y17" s="97" t="s">
+      <c r="Y50" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="Z17" s="98"/>
-    </row>
-    <row r="18" spans="2:26" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="47" t="s">
+      <c r="Z50" s="46"/>
+    </row>
+    <row r="51" spans="2:26" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B51" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="48"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="53" t="s">
+      <c r="C51" s="51"/>
+      <c r="D51" s="51"/>
+      <c r="E51" s="52"/>
+      <c r="F51" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="G18" s="54"/>
-      <c r="H18" s="54"/>
-      <c r="I18" s="54"/>
-      <c r="J18" s="54"/>
-      <c r="K18" s="55"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="10"/>
-      <c r="O18" s="111"/>
-      <c r="P18" s="112"/>
-      <c r="Q18" s="11"/>
-      <c r="R18" s="100"/>
-      <c r="S18" s="121"/>
-      <c r="T18" s="123"/>
-      <c r="U18" s="124"/>
-      <c r="V18" s="125"/>
-      <c r="W18" s="121"/>
-      <c r="X18" s="121"/>
-      <c r="Y18" s="123"/>
-      <c r="Z18" s="125"/>
-    </row>
-    <row r="19" spans="2:26" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="50"/>
-      <c r="C19" s="51"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="52"/>
-      <c r="F19" s="56" t="s">
+      <c r="G51" s="62"/>
+      <c r="H51" s="62"/>
+      <c r="I51" s="62"/>
+      <c r="J51" s="62"/>
+      <c r="K51" s="63"/>
+      <c r="L51" s="6"/>
+      <c r="M51" s="6"/>
+      <c r="N51" s="8"/>
+      <c r="O51" s="115"/>
+      <c r="P51" s="116"/>
+      <c r="Q51" s="9"/>
+      <c r="R51" s="48"/>
+      <c r="S51" s="127"/>
+      <c r="T51" s="129"/>
+      <c r="U51" s="130"/>
+      <c r="V51" s="131"/>
+      <c r="W51" s="127" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="X51" s="127"/>
+      <c r="Y51" s="129"/>
+      <c r="Z51" s="131"/>
+    </row>
+    <row r="52" spans="2:26" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="53"/>
+      <c r="C52" s="54"/>
+      <c r="D52" s="54"/>
+      <c r="E52" s="55"/>
+      <c r="F52" s="84" t="s">
         <v>8</v>
       </c>
-      <c r="G19" s="57"/>
-      <c r="H19" s="57"/>
-      <c r="I19" s="57"/>
-      <c r="J19" s="57"/>
-      <c r="K19" s="58"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="113"/>
-      <c r="P19" s="114"/>
-      <c r="Q19" s="11"/>
-      <c r="R19" s="101"/>
-      <c r="S19" s="122"/>
-      <c r="T19" s="126"/>
-      <c r="U19" s="127"/>
-      <c r="V19" s="128"/>
-      <c r="W19" s="122"/>
-      <c r="X19" s="122"/>
-      <c r="Y19" s="126"/>
-      <c r="Z19" s="128"/>
+      <c r="G52" s="85"/>
+      <c r="H52" s="85"/>
+      <c r="I52" s="85"/>
+      <c r="J52" s="85"/>
+      <c r="K52" s="86"/>
+      <c r="L52" s="6"/>
+      <c r="M52" s="7"/>
+      <c r="N52" s="9"/>
+      <c r="O52" s="144"/>
+      <c r="P52" s="145"/>
+      <c r="Q52" s="9"/>
+      <c r="R52" s="49"/>
+      <c r="S52" s="128"/>
+      <c r="T52" s="132"/>
+      <c r="U52" s="133"/>
+      <c r="V52" s="134"/>
+      <c r="W52" s="128"/>
+      <c r="X52" s="128"/>
+      <c r="Y52" s="132"/>
+      <c r="Z52" s="134"/>
+    </row>
+    <row r="57" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="C57" s="44"/>
+      <c r="D57" s="44"/>
+    </row>
+    <row r="58" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="C58" s="44"/>
+      <c r="D58" s="44"/>
+    </row>
+    <row r="59" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="C59" s="44"/>
+      <c r="D59" s="44"/>
+    </row>
+    <row r="63" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="C63" s="17"/>
+    </row>
+    <row r="64" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="C64" s="17"/>
+    </row>
+    <row r="65" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C65" s="17"/>
+    </row>
+    <row r="66" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C66" s="17"/>
+    </row>
+    <row r="72" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E72" s="23"/>
     </row>
   </sheetData>
-  <mergeCells count="62">
-    <mergeCell ref="V8:Z8"/>
-    <mergeCell ref="V9:Z9"/>
-    <mergeCell ref="V10:Z10"/>
+  <mergeCells count="175">
+    <mergeCell ref="T16:Z24"/>
+    <mergeCell ref="R16:S24"/>
+    <mergeCell ref="T25:Z33"/>
+    <mergeCell ref="R25:S33"/>
+    <mergeCell ref="G16:K16"/>
+    <mergeCell ref="G50:K50"/>
+    <mergeCell ref="G49:K49"/>
+    <mergeCell ref="G48:K48"/>
+    <mergeCell ref="G47:K47"/>
+    <mergeCell ref="G46:K46"/>
+    <mergeCell ref="G45:K45"/>
+    <mergeCell ref="G44:K44"/>
+    <mergeCell ref="G43:K43"/>
+    <mergeCell ref="G42:K42"/>
+    <mergeCell ref="G41:K41"/>
+    <mergeCell ref="G40:K40"/>
+    <mergeCell ref="G39:K39"/>
+    <mergeCell ref="G38:K38"/>
+    <mergeCell ref="G37:K37"/>
+    <mergeCell ref="G36:K36"/>
+    <mergeCell ref="G35:K35"/>
+    <mergeCell ref="G34:K34"/>
+    <mergeCell ref="G33:K33"/>
+    <mergeCell ref="G32:K32"/>
+    <mergeCell ref="G31:K31"/>
+    <mergeCell ref="G30:K30"/>
+    <mergeCell ref="G29:K29"/>
+    <mergeCell ref="G28:K28"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C50:F50"/>
+    <mergeCell ref="C49:F49"/>
+    <mergeCell ref="C48:F48"/>
+    <mergeCell ref="C47:F47"/>
+    <mergeCell ref="C46:F46"/>
+    <mergeCell ref="C45:F45"/>
+    <mergeCell ref="C44:F44"/>
+    <mergeCell ref="C43:F43"/>
+    <mergeCell ref="C42:F42"/>
+    <mergeCell ref="C41:F41"/>
+    <mergeCell ref="C40:F40"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="G14:K15"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="G27:K27"/>
+    <mergeCell ref="G26:K26"/>
+    <mergeCell ref="G25:K25"/>
+    <mergeCell ref="G24:K24"/>
+    <mergeCell ref="G23:K23"/>
+    <mergeCell ref="G22:K22"/>
     <mergeCell ref="B2:Z2"/>
-    <mergeCell ref="S18:S19"/>
-    <mergeCell ref="T18:V19"/>
-    <mergeCell ref="W18:W19"/>
-    <mergeCell ref="X18:X19"/>
-    <mergeCell ref="Y18:Z19"/>
+    <mergeCell ref="S51:S52"/>
+    <mergeCell ref="T51:V52"/>
+    <mergeCell ref="W51:W52"/>
+    <mergeCell ref="X51:X52"/>
+    <mergeCell ref="Y51:Z52"/>
     <mergeCell ref="M7:U7"/>
     <mergeCell ref="M8:U8"/>
     <mergeCell ref="M9:U9"/>
     <mergeCell ref="M10:U10"/>
     <mergeCell ref="V7:Z7"/>
-    <mergeCell ref="H17:K17"/>
-    <mergeCell ref="P11:T11"/>
-    <mergeCell ref="P12:T12"/>
-    <mergeCell ref="U11:W11"/>
     <mergeCell ref="U12:W12"/>
+    <mergeCell ref="O52:P52"/>
     <mergeCell ref="X11:Z11"/>
-    <mergeCell ref="Y17:Z17"/>
-    <mergeCell ref="R17:R19"/>
-    <mergeCell ref="T17:V17"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="R14:Z15"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="O15:P15"/>
-    <mergeCell ref="L14:Q14"/>
-    <mergeCell ref="J11:O11"/>
-    <mergeCell ref="J12:O12"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H16:K16"/>
-    <mergeCell ref="H14:K15"/>
     <mergeCell ref="K7:L7"/>
     <mergeCell ref="K8:L8"/>
     <mergeCell ref="K9:L9"/>
     <mergeCell ref="K10:L10"/>
-    <mergeCell ref="B18:E19"/>
-    <mergeCell ref="F18:K18"/>
-    <mergeCell ref="F19:K19"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="G10:J10"/>
+    <mergeCell ref="P11:T11"/>
+    <mergeCell ref="J11:O11"/>
+    <mergeCell ref="V8:Z8"/>
+    <mergeCell ref="V9:Z9"/>
+    <mergeCell ref="V10:Z10"/>
+    <mergeCell ref="U11:W11"/>
     <mergeCell ref="G9:J9"/>
     <mergeCell ref="G7:J7"/>
     <mergeCell ref="G8:J8"/>
+    <mergeCell ref="T50:V50"/>
+    <mergeCell ref="O51:P51"/>
+    <mergeCell ref="P12:T12"/>
+    <mergeCell ref="O50:P50"/>
+    <mergeCell ref="O15:P15"/>
+    <mergeCell ref="L14:Q14"/>
+    <mergeCell ref="R14:Z15"/>
+    <mergeCell ref="O41:P41"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="F52:K52"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="G10:J10"/>
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="G12:H12"/>
+    <mergeCell ref="J12:O12"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B12:C12"/>
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="D12:F12"/>
     <mergeCell ref="B9:D9"/>
@@ -2425,6 +3710,57 @@
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="E10:F10"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="C57:D59"/>
+    <mergeCell ref="Y50:Z50"/>
+    <mergeCell ref="R50:R52"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="B51:E52"/>
+    <mergeCell ref="T35:X35"/>
+    <mergeCell ref="U42:X42"/>
+    <mergeCell ref="U43:X43"/>
+    <mergeCell ref="U44:X44"/>
+    <mergeCell ref="U45:X45"/>
+    <mergeCell ref="U47:X47"/>
+    <mergeCell ref="U48:X48"/>
+    <mergeCell ref="U46:X46"/>
+    <mergeCell ref="S44:S47"/>
+    <mergeCell ref="F51:K51"/>
+    <mergeCell ref="O49:P49"/>
+    <mergeCell ref="O48:P48"/>
+    <mergeCell ref="O47:P47"/>
+    <mergeCell ref="O46:P46"/>
+    <mergeCell ref="O45:P45"/>
+    <mergeCell ref="O44:P44"/>
+    <mergeCell ref="O43:P43"/>
+    <mergeCell ref="O42:P42"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="O37:P37"/>
+    <mergeCell ref="O36:P36"/>
+    <mergeCell ref="O35:P35"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="O28:P28"/>
+    <mergeCell ref="O27:P27"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="O25:P25"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="O23:P23"/>
+    <mergeCell ref="O22:P22"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="G21:K21"/>
+    <mergeCell ref="G20:K20"/>
+    <mergeCell ref="G19:K19"/>
+    <mergeCell ref="G18:K18"/>
+    <mergeCell ref="G17:K17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
